--- a/Balanced_Timetable_latest.xlsx
+++ b/Balanced_Timetable_latest.xlsx
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="CSE-I Timetable" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="DSAI-I Timetable" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="ECE-I Timetable" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="CSE-III Timetable" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="DSAI-III Timetable" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="ECE-III Timetable" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="CSE-V Timetable" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="DSAI-V Timetable" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="ECE-V Timetable" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="COMMON 7TH-SEM Timetable" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CSE-I Timetable" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DSAI-I Timetable" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ECE-I Timetable" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CSE-III Timetable" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DSAI-III Timetable" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ECE-III Timetable" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CSE-V Timetable" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DSAI-V Timetable" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ECE-V Timetable" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COMMON 7TH-SEM Timetable" sheetId="10" state="visible" r:id="rId10"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -8236,13 +8236,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T70"/>
+  <dimension ref="A1:T66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
     <col width="46" customWidth="1" min="2" max="2"/>
     <col width="15" customWidth="1" min="3" max="3"/>
-    <col width="25" customWidth="1" min="4" max="4"/>
+    <col width="23" customWidth="1" min="4" max="4"/>
     <col width="15" customWidth="1" min="5" max="5"/>
     <col width="18" customWidth="1" min="6" max="6"/>
     <col width="17" customWidth="1" min="7" max="7"/>
@@ -9081,22 +9081,22 @@
     <row r="23">
       <c r="A23" s="16" t="inlineStr">
         <is>
-          <t>MA261</t>
+          <t>CS261</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>Differential Equations</t>
+          <t>Operating Systems</t>
         </is>
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>3-1-0-0-2</t>
+          <t>3-1-0-4-2</t>
         </is>
       </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t>Dr. Anand Barangi</t>
+          <t>Dr. Suvadip Hazra</t>
         </is>
       </c>
       <c r="E23" s="3" t="inlineStr">
@@ -9131,27 +9131,27 @@
     <row r="24">
       <c r="A24" s="16" t="inlineStr">
         <is>
-          <t>MA262</t>
+          <t>CS262</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>Multivariate Calculus</t>
+          <t>Software design tools and technique</t>
         </is>
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t>3-1-0-0-2</t>
+          <t>3-0-2-0-3</t>
         </is>
       </c>
       <c r="D24" s="3" t="inlineStr">
         <is>
-          <t>Dr. Somen Bhattacharjee</t>
+          <t>Dr. Sunil Kumar P V</t>
         </is>
       </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
-          <t>Second Half</t>
+          <t>Full Sem</t>
         </is>
       </c>
       <c r="F24" s="3" t="inlineStr">
@@ -9181,27 +9181,27 @@
     <row r="25">
       <c r="A25" s="16" t="inlineStr">
         <is>
-          <t>CS261</t>
+          <t>CS263</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>Operating Systems</t>
+          <t>Design &amp; Analysis of Algorithms</t>
         </is>
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>3-1-0-4-2</t>
+          <t>3-0-2-0-4</t>
         </is>
       </c>
       <c r="D25" s="3" t="inlineStr">
         <is>
-          <t>Dr. Suvadip Hazra</t>
+          <t>Dr. Malay</t>
         </is>
       </c>
       <c r="E25" s="3" t="inlineStr">
         <is>
-          <t>First Half</t>
+          <t>Full Sem</t>
         </is>
       </c>
       <c r="F25" s="3" t="inlineStr">
@@ -9231,22 +9231,22 @@
     <row r="26">
       <c r="A26" s="16" t="inlineStr">
         <is>
-          <t>CS262</t>
+          <t>CS264</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>Software design tools and technique</t>
+          <t>Computer Networks</t>
         </is>
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t>3-0-2-0-3</t>
+          <t>3-1-0-0-4</t>
         </is>
       </c>
       <c r="D26" s="3" t="inlineStr">
         <is>
-          <t>Dr. Sunil Kumar P V</t>
+          <t>Dr. Prabhu Prasad BM</t>
         </is>
       </c>
       <c r="E26" s="3" t="inlineStr">
@@ -9281,40 +9281,44 @@
     <row r="27">
       <c r="A27" s="16" t="inlineStr">
         <is>
-          <t>CS263</t>
+          <t>EC251</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>Design &amp; Analysis of Algorithms</t>
+          <t>Electronics System Design-I</t>
         </is>
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t>3-0-2-0-4</t>
+          <t>3-1-0-0-2</t>
         </is>
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t>Dr. Malay</t>
+          <t>Dr. Pankaj Kumar</t>
         </is>
       </c>
       <c r="E27" s="3" t="inlineStr">
         <is>
-          <t>Full Sem</t>
+          <t>First Half</t>
         </is>
       </c>
       <c r="F27" s="3" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G27" s="3" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H27" s="4" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H27" s="3" t="inlineStr">
+        <is>
+          <t>C301</t>
+        </is>
+      </c>
       <c r="I27" s="4" t="n"/>
       <c r="J27" s="4" t="n"/>
       <c r="K27" s="4" t="n"/>
@@ -9331,40 +9335,44 @@
     <row r="28">
       <c r="A28" s="16" t="inlineStr">
         <is>
-          <t>CS264</t>
+          <t>EC252</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>Computer Networks</t>
+          <t>Introduction of RFIC design</t>
         </is>
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t>3-1-0-0-4</t>
+          <t>3-1-0-0-2</t>
         </is>
       </c>
       <c r="D28" s="3" t="inlineStr">
         <is>
-          <t>Dr. Prabhu Prasad BM</t>
+          <t>Dr. Rajesh Kumar</t>
         </is>
       </c>
       <c r="E28" s="3" t="inlineStr">
         <is>
-          <t>Full Sem</t>
+          <t>Second Half</t>
         </is>
       </c>
       <c r="F28" s="3" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G28" s="3" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H28" s="4" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H28" s="3" t="inlineStr">
+        <is>
+          <t>C102</t>
+        </is>
+      </c>
       <c r="I28" s="4" t="n"/>
       <c r="J28" s="4" t="n"/>
       <c r="K28" s="4" t="n"/>
@@ -9381,12 +9389,12 @@
     <row r="29">
       <c r="A29" s="16" t="inlineStr">
         <is>
-          <t>EC251</t>
+          <t>EC253</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>Electronics System Design-I</t>
+          <t>Introduction to Embedded Signal Intelligence</t>
         </is>
       </c>
       <c r="C29" s="3" t="inlineStr">
@@ -9396,12 +9404,12 @@
       </c>
       <c r="D29" s="3" t="inlineStr">
         <is>
-          <t>Dr. Pankaj Kumar</t>
+          <t>Dr. Sibasankar Padhy</t>
         </is>
       </c>
       <c r="E29" s="3" t="inlineStr">
         <is>
-          <t>First Half</t>
+          <t>Second Half</t>
         </is>
       </c>
       <c r="F29" s="3" t="inlineStr">
@@ -9416,7 +9424,7 @@
       </c>
       <c r="H29" s="3" t="inlineStr">
         <is>
-          <t>C301</t>
+          <t>C401</t>
         </is>
       </c>
       <c r="I29" s="4" t="n"/>
@@ -9435,12 +9443,12 @@
     <row r="30">
       <c r="A30" s="16" t="inlineStr">
         <is>
-          <t>EC252</t>
+          <t>EC254</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>Introduction of RFIC design</t>
+          <t>Electronic Systems Engineering</t>
         </is>
       </c>
       <c r="C30" s="3" t="inlineStr">
@@ -9450,12 +9458,12 @@
       </c>
       <c r="D30" s="3" t="inlineStr">
         <is>
-          <t>Dr. Rajesh Kumar</t>
+          <t>Mr. Mallikarjun Kande</t>
         </is>
       </c>
       <c r="E30" s="3" t="inlineStr">
         <is>
-          <t>Second Half</t>
+          <t>First Half</t>
         </is>
       </c>
       <c r="F30" s="3" t="inlineStr">
@@ -9470,7 +9478,7 @@
       </c>
       <c r="H30" s="3" t="inlineStr">
         <is>
-          <t>C102</t>
+          <t>C003</t>
         </is>
       </c>
       <c r="I30" s="4" t="n"/>
@@ -9489,12 +9497,12 @@
     <row r="31">
       <c r="A31" s="16" t="inlineStr">
         <is>
-          <t>EC253</t>
+          <t>CS152</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>Introduction to Embedded Signal Intelligence</t>
+          <t>Data Science with Python</t>
         </is>
       </c>
       <c r="C31" s="3" t="inlineStr">
@@ -9504,12 +9512,12 @@
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t>Dr. Sibasankar Padhy</t>
+          <t>Dr. Abdul Wahid</t>
         </is>
       </c>
       <c r="E31" s="3" t="inlineStr">
         <is>
-          <t>Second Half</t>
+          <t>First Half</t>
         </is>
       </c>
       <c r="F31" s="3" t="inlineStr">
@@ -9524,7 +9532,7 @@
       </c>
       <c r="H31" s="3" t="inlineStr">
         <is>
-          <t>C401</t>
+          <t>C302</t>
         </is>
       </c>
       <c r="I31" s="4" t="n"/>
@@ -9543,12 +9551,12 @@
     <row r="32">
       <c r="A32" s="16" t="inlineStr">
         <is>
-          <t>EC254</t>
+          <t>CS251</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>Electronic Systems Engineering</t>
+          <t>2D Computer Graphics</t>
         </is>
       </c>
       <c r="C32" s="3" t="inlineStr">
@@ -9558,7 +9566,7 @@
       </c>
       <c r="D32" s="3" t="inlineStr">
         <is>
-          <t>Mr. Mallikarjun Kande</t>
+          <t>Dr. Vivekraj V K</t>
         </is>
       </c>
       <c r="E32" s="3" t="inlineStr">
@@ -9578,7 +9586,7 @@
       </c>
       <c r="H32" s="3" t="inlineStr">
         <is>
-          <t>C003</t>
+          <t>C303</t>
         </is>
       </c>
       <c r="I32" s="4" t="n"/>
@@ -9595,46 +9603,14 @@
       <c r="T32" s="4" t="n"/>
     </row>
     <row r="33">
-      <c r="A33" s="16" t="inlineStr">
-        <is>
-          <t>CS152</t>
-        </is>
-      </c>
-      <c r="B33" s="3" t="inlineStr">
-        <is>
-          <t>Data Science with Python</t>
-        </is>
-      </c>
-      <c r="C33" s="3" t="inlineStr">
-        <is>
-          <t>3-1-0-0-2</t>
-        </is>
-      </c>
-      <c r="D33" s="3" t="inlineStr">
-        <is>
-          <t>Dr. Abdul Wahid</t>
-        </is>
-      </c>
-      <c r="E33" s="3" t="inlineStr">
-        <is>
-          <t>First Half</t>
-        </is>
-      </c>
-      <c r="F33" s="3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G33" s="3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H33" s="3" t="inlineStr">
-        <is>
-          <t>C302</t>
-        </is>
-      </c>
+      <c r="A33" t="inlineStr"/>
+      <c r="B33" s="4" t="n"/>
+      <c r="C33" s="4" t="n"/>
+      <c r="D33" s="4" t="n"/>
+      <c r="E33" s="4" t="n"/>
+      <c r="F33" s="4" t="n"/>
+      <c r="G33" s="4" t="n"/>
+      <c r="H33" s="4" t="n"/>
       <c r="I33" s="4" t="n"/>
       <c r="J33" s="4" t="n"/>
       <c r="K33" s="4" t="n"/>
@@ -9649,46 +9625,14 @@
       <c r="T33" s="4" t="n"/>
     </row>
     <row r="34">
-      <c r="A34" s="16" t="inlineStr">
-        <is>
-          <t>CS251</t>
-        </is>
-      </c>
-      <c r="B34" s="3" t="inlineStr">
-        <is>
-          <t>2D Computer Graphics</t>
-        </is>
-      </c>
-      <c r="C34" s="3" t="inlineStr">
-        <is>
-          <t>3-1-0-0-2</t>
-        </is>
-      </c>
-      <c r="D34" s="3" t="inlineStr">
-        <is>
-          <t>Dr. Vivekraj V K</t>
-        </is>
-      </c>
-      <c r="E34" s="3" t="inlineStr">
-        <is>
-          <t>First Half</t>
-        </is>
-      </c>
-      <c r="F34" s="3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G34" s="3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H34" s="3" t="inlineStr">
-        <is>
-          <t>C303</t>
-        </is>
-      </c>
+      <c r="A34" t="inlineStr"/>
+      <c r="B34" s="4" t="n"/>
+      <c r="C34" s="4" t="n"/>
+      <c r="D34" s="4" t="n"/>
+      <c r="E34" s="4" t="n"/>
+      <c r="F34" s="4" t="n"/>
+      <c r="G34" s="4" t="n"/>
+      <c r="H34" s="4" t="n"/>
       <c r="I34" s="4" t="n"/>
       <c r="J34" s="4" t="n"/>
       <c r="K34" s="4" t="n"/>
@@ -9703,7 +9647,11 @@
       <c r="T34" s="4" t="n"/>
     </row>
     <row r="35">
-      <c r="A35" t="inlineStr"/>
+      <c r="A35" s="1" t="inlineStr">
+        <is>
+          <t>CSEB III First Half</t>
+        </is>
+      </c>
       <c r="B35" s="4" t="n"/>
       <c r="C35" s="4" t="n"/>
       <c r="D35" s="4" t="n"/>
@@ -9725,186 +9673,210 @@
       <c r="T35" s="4" t="n"/>
     </row>
     <row r="36">
-      <c r="A36" t="inlineStr"/>
-      <c r="B36" s="4" t="n"/>
-      <c r="C36" s="4" t="n"/>
-      <c r="D36" s="4" t="n"/>
-      <c r="E36" s="4" t="n"/>
-      <c r="F36" s="4" t="n"/>
-      <c r="G36" s="4" t="n"/>
-      <c r="H36" s="4" t="n"/>
-      <c r="I36" s="4" t="n"/>
-      <c r="J36" s="4" t="n"/>
-      <c r="K36" s="4" t="n"/>
-      <c r="L36" s="4" t="n"/>
-      <c r="M36" s="4" t="n"/>
-      <c r="N36" s="4" t="n"/>
-      <c r="O36" s="4" t="n"/>
-      <c r="P36" s="4" t="n"/>
-      <c r="Q36" s="4" t="n"/>
-      <c r="R36" s="4" t="n"/>
-      <c r="S36" s="4" t="n"/>
-      <c r="T36" s="4" t="n"/>
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Day</t>
+        </is>
+      </c>
+      <c r="B36" s="3" t="inlineStr">
+        <is>
+          <t>07:30-09:00</t>
+        </is>
+      </c>
+      <c r="C36" s="3" t="inlineStr">
+        <is>
+          <t>09:00-10:00</t>
+        </is>
+      </c>
+      <c r="D36" s="3" t="inlineStr">
+        <is>
+          <t>10:00-10:30</t>
+        </is>
+      </c>
+      <c r="E36" s="3" t="inlineStr">
+        <is>
+          <t>10:30-10:45</t>
+        </is>
+      </c>
+      <c r="F36" s="3" t="inlineStr">
+        <is>
+          <t>10:45-11:00</t>
+        </is>
+      </c>
+      <c r="G36" s="3" t="inlineStr">
+        <is>
+          <t>11:00-12:00</t>
+        </is>
+      </c>
+      <c r="H36" s="3" t="inlineStr">
+        <is>
+          <t>12:00-12:15</t>
+        </is>
+      </c>
+      <c r="I36" s="3" t="inlineStr">
+        <is>
+          <t>12:15-12:30</t>
+        </is>
+      </c>
+      <c r="J36" s="3" t="inlineStr">
+        <is>
+          <t>12:30-12:45</t>
+        </is>
+      </c>
+      <c r="K36" s="3" t="inlineStr">
+        <is>
+          <t>12:45-13:15</t>
+        </is>
+      </c>
+      <c r="L36" s="3" t="inlineStr">
+        <is>
+          <t>13:15-14:00</t>
+        </is>
+      </c>
+      <c r="M36" s="3" t="inlineStr">
+        <is>
+          <t>14:00-14:30</t>
+        </is>
+      </c>
+      <c r="N36" s="3" t="inlineStr">
+        <is>
+          <t>14:30-15:30</t>
+        </is>
+      </c>
+      <c r="O36" s="3" t="inlineStr">
+        <is>
+          <t>15:30-15:40</t>
+        </is>
+      </c>
+      <c r="P36" s="3" t="inlineStr">
+        <is>
+          <t>15:40-16:00</t>
+        </is>
+      </c>
+      <c r="Q36" s="3" t="inlineStr">
+        <is>
+          <t>16:00-16:30</t>
+        </is>
+      </c>
+      <c r="R36" s="3" t="inlineStr">
+        <is>
+          <t>16:30-17:10</t>
+        </is>
+      </c>
+      <c r="S36" s="3" t="inlineStr">
+        <is>
+          <t>17:10-17:30</t>
+        </is>
+      </c>
+      <c r="T36" s="3" t="inlineStr">
+        <is>
+          <t>17:30-18:30</t>
+        </is>
+      </c>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="inlineStr">
-        <is>
-          <t>CSEB III First Half</t>
-        </is>
-      </c>
-      <c r="B37" s="4" t="n"/>
-      <c r="C37" s="4" t="n"/>
-      <c r="D37" s="4" t="n"/>
-      <c r="E37" s="4" t="n"/>
-      <c r="F37" s="4" t="n"/>
-      <c r="G37" s="4" t="n"/>
-      <c r="H37" s="4" t="n"/>
-      <c r="I37" s="4" t="n"/>
-      <c r="J37" s="4" t="n"/>
-      <c r="K37" s="4" t="n"/>
-      <c r="L37" s="4" t="n"/>
-      <c r="M37" s="4" t="n"/>
-      <c r="N37" s="4" t="n"/>
-      <c r="O37" s="4" t="n"/>
-      <c r="P37" s="4" t="n"/>
-      <c r="Q37" s="4" t="n"/>
-      <c r="R37" s="4" t="n"/>
-      <c r="S37" s="4" t="n"/>
-      <c r="T37" s="4" t="n"/>
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Monday</t>
+        </is>
+      </c>
+      <c r="B37" s="4" t="inlineStr"/>
+      <c r="C37" s="5" t="inlineStr">
+        <is>
+          <t>Elective1</t>
+        </is>
+      </c>
+      <c r="D37" s="5" t="n"/>
+      <c r="E37" s="4" t="inlineStr"/>
+      <c r="F37" s="17" t="inlineStr">
+        <is>
+          <t>CS262 (Lab-L206)</t>
+        </is>
+      </c>
+      <c r="G37" s="17" t="n"/>
+      <c r="H37" s="17" t="n"/>
+      <c r="I37" s="17" t="n"/>
+      <c r="J37" s="17" t="n"/>
+      <c r="K37" s="4" t="inlineStr"/>
+      <c r="L37" s="4" t="inlineStr"/>
+      <c r="M37" s="18" t="inlineStr">
+        <is>
+          <t>CS264 (C204)</t>
+        </is>
+      </c>
+      <c r="N37" s="18" t="n"/>
+      <c r="O37" s="4" t="inlineStr"/>
+      <c r="P37" s="4" t="inlineStr"/>
+      <c r="Q37" s="4" t="inlineStr"/>
+      <c r="R37" s="4" t="inlineStr"/>
+      <c r="S37" s="4" t="inlineStr"/>
+      <c r="T37" s="4" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Day</t>
-        </is>
-      </c>
-      <c r="B38" s="3" t="inlineStr">
-        <is>
-          <t>07:30-09:00</t>
-        </is>
-      </c>
-      <c r="C38" s="3" t="inlineStr">
-        <is>
-          <t>09:00-10:00</t>
-        </is>
-      </c>
-      <c r="D38" s="3" t="inlineStr">
-        <is>
-          <t>10:00-10:30</t>
-        </is>
-      </c>
-      <c r="E38" s="3" t="inlineStr">
-        <is>
-          <t>10:30-10:45</t>
-        </is>
-      </c>
-      <c r="F38" s="3" t="inlineStr">
-        <is>
-          <t>10:45-11:00</t>
-        </is>
-      </c>
-      <c r="G38" s="3" t="inlineStr">
-        <is>
-          <t>11:00-12:00</t>
-        </is>
-      </c>
-      <c r="H38" s="3" t="inlineStr">
-        <is>
-          <t>12:00-12:15</t>
-        </is>
-      </c>
-      <c r="I38" s="3" t="inlineStr">
-        <is>
-          <t>12:15-12:30</t>
-        </is>
-      </c>
-      <c r="J38" s="3" t="inlineStr">
-        <is>
-          <t>12:30-12:45</t>
-        </is>
-      </c>
-      <c r="K38" s="3" t="inlineStr">
-        <is>
-          <t>12:45-13:15</t>
-        </is>
-      </c>
-      <c r="L38" s="3" t="inlineStr">
-        <is>
-          <t>13:15-14:00</t>
-        </is>
-      </c>
-      <c r="M38" s="3" t="inlineStr">
-        <is>
-          <t>14:00-14:30</t>
-        </is>
-      </c>
-      <c r="N38" s="3" t="inlineStr">
-        <is>
-          <t>14:30-15:30</t>
-        </is>
-      </c>
-      <c r="O38" s="3" t="inlineStr">
-        <is>
-          <t>15:30-15:40</t>
-        </is>
-      </c>
-      <c r="P38" s="3" t="inlineStr">
-        <is>
-          <t>15:40-16:00</t>
-        </is>
-      </c>
-      <c r="Q38" s="3" t="inlineStr">
-        <is>
-          <t>16:00-16:30</t>
-        </is>
-      </c>
-      <c r="R38" s="3" t="inlineStr">
-        <is>
-          <t>16:30-17:10</t>
-        </is>
-      </c>
-      <c r="S38" s="3" t="inlineStr">
-        <is>
-          <t>17:10-17:30</t>
-        </is>
-      </c>
-      <c r="T38" s="3" t="inlineStr">
-        <is>
-          <t>17:30-18:30</t>
-        </is>
-      </c>
+          <t>Tuesday</t>
+        </is>
+      </c>
+      <c r="B38" s="4" t="inlineStr"/>
+      <c r="C38" s="5" t="inlineStr">
+        <is>
+          <t>Elective1</t>
+        </is>
+      </c>
+      <c r="D38" s="5" t="n"/>
+      <c r="E38" s="4" t="inlineStr"/>
+      <c r="F38" s="20" t="inlineStr">
+        <is>
+          <t>CS263 (C204)</t>
+        </is>
+      </c>
+      <c r="G38" s="20" t="n"/>
+      <c r="H38" s="20" t="n"/>
+      <c r="I38" s="18" t="inlineStr">
+        <is>
+          <t>CS264T (C205)</t>
+        </is>
+      </c>
+      <c r="J38" s="18" t="n"/>
+      <c r="K38" s="18" t="n"/>
+      <c r="L38" s="4" t="inlineStr"/>
+      <c r="M38" s="4" t="inlineStr"/>
+      <c r="N38" s="4" t="inlineStr"/>
+      <c r="O38" s="4" t="inlineStr"/>
+      <c r="P38" s="4" t="inlineStr"/>
+      <c r="Q38" s="4" t="inlineStr"/>
+      <c r="R38" s="4" t="inlineStr"/>
+      <c r="S38" s="4" t="inlineStr"/>
+      <c r="T38" s="4" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Monday</t>
+          <t>Wednesday</t>
         </is>
       </c>
       <c r="B39" s="4" t="inlineStr"/>
       <c r="C39" s="5" t="inlineStr">
         <is>
-          <t>Elective1</t>
-        </is>
-      </c>
-      <c r="D39" s="5" t="n"/>
+          <t>Elective1T</t>
+        </is>
+      </c>
+      <c r="D39" s="4" t="inlineStr"/>
       <c r="E39" s="4" t="inlineStr"/>
-      <c r="F39" s="17" t="inlineStr">
-        <is>
-          <t>CS262 (Lab-L206)</t>
-        </is>
-      </c>
-      <c r="G39" s="17" t="n"/>
-      <c r="H39" s="17" t="n"/>
-      <c r="I39" s="17" t="n"/>
-      <c r="J39" s="17" t="n"/>
+      <c r="F39" s="20" t="inlineStr">
+        <is>
+          <t>CS263 (C204)</t>
+        </is>
+      </c>
+      <c r="G39" s="20" t="n"/>
+      <c r="H39" s="20" t="n"/>
+      <c r="I39" s="4" t="inlineStr"/>
+      <c r="J39" s="4" t="inlineStr"/>
       <c r="K39" s="4" t="inlineStr"/>
       <c r="L39" s="4" t="inlineStr"/>
-      <c r="M39" s="18" t="inlineStr">
-        <is>
-          <t>CS264 (C204)</t>
-        </is>
-      </c>
-      <c r="N39" s="18" t="n"/>
+      <c r="M39" s="4" t="inlineStr"/>
+      <c r="N39" s="4" t="inlineStr"/>
       <c r="O39" s="4" t="inlineStr"/>
       <c r="P39" s="4" t="inlineStr"/>
       <c r="Q39" s="4" t="inlineStr"/>
@@ -9915,31 +9887,27 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Tuesday</t>
+          <t>Thursday</t>
         </is>
       </c>
       <c r="B40" s="4" t="inlineStr"/>
-      <c r="C40" s="5" t="inlineStr">
-        <is>
-          <t>Elective1</t>
-        </is>
-      </c>
-      <c r="D40" s="5" t="n"/>
+      <c r="C40" s="17" t="inlineStr">
+        <is>
+          <t>CS262 (C202)</t>
+        </is>
+      </c>
+      <c r="D40" s="17" t="n"/>
       <c r="E40" s="4" t="inlineStr"/>
       <c r="F40" s="20" t="inlineStr">
         <is>
-          <t>CS263 (C204)</t>
+          <t>CS263 (Lab-L207)</t>
         </is>
       </c>
       <c r="G40" s="20" t="n"/>
       <c r="H40" s="20" t="n"/>
-      <c r="I40" s="18" t="inlineStr">
-        <is>
-          <t>CS264T (C205)</t>
-        </is>
-      </c>
-      <c r="J40" s="18" t="n"/>
-      <c r="K40" s="18" t="n"/>
+      <c r="I40" s="20" t="n"/>
+      <c r="J40" s="20" t="n"/>
+      <c r="K40" s="4" t="inlineStr"/>
       <c r="L40" s="4" t="inlineStr"/>
       <c r="M40" s="4" t="inlineStr"/>
       <c r="N40" s="4" t="inlineStr"/>
@@ -9953,24 +9921,24 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Wednesday</t>
+          <t>Friday</t>
         </is>
       </c>
       <c r="B41" s="4" t="inlineStr"/>
-      <c r="C41" s="5" t="inlineStr">
-        <is>
-          <t>Elective1T</t>
-        </is>
-      </c>
-      <c r="D41" s="4" t="inlineStr"/>
+      <c r="C41" s="17" t="inlineStr">
+        <is>
+          <t>CS262 (C202)</t>
+        </is>
+      </c>
+      <c r="D41" s="17" t="n"/>
       <c r="E41" s="4" t="inlineStr"/>
-      <c r="F41" s="20" t="inlineStr">
-        <is>
-          <t>CS263 (C204)</t>
-        </is>
-      </c>
-      <c r="G41" s="20" t="n"/>
-      <c r="H41" s="20" t="n"/>
+      <c r="F41" s="18" t="inlineStr">
+        <is>
+          <t>CS264 (C204)</t>
+        </is>
+      </c>
+      <c r="G41" s="18" t="n"/>
+      <c r="H41" s="18" t="n"/>
       <c r="I41" s="4" t="inlineStr"/>
       <c r="J41" s="4" t="inlineStr"/>
       <c r="K41" s="4" t="inlineStr"/>
@@ -9985,75 +9953,55 @@
       <c r="T41" s="4" t="inlineStr"/>
     </row>
     <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>Thursday</t>
-        </is>
-      </c>
-      <c r="B42" s="4" t="inlineStr"/>
-      <c r="C42" s="17" t="inlineStr">
-        <is>
-          <t>CS262 (C202)</t>
-        </is>
-      </c>
-      <c r="D42" s="17" t="n"/>
-      <c r="E42" s="4" t="inlineStr"/>
-      <c r="F42" s="20" t="inlineStr">
-        <is>
-          <t>CS263 (Lab-L207)</t>
-        </is>
-      </c>
-      <c r="G42" s="20" t="n"/>
-      <c r="H42" s="20" t="n"/>
-      <c r="I42" s="20" t="n"/>
-      <c r="J42" s="20" t="n"/>
-      <c r="K42" s="4" t="inlineStr"/>
-      <c r="L42" s="4" t="inlineStr"/>
-      <c r="M42" s="4" t="inlineStr"/>
-      <c r="N42" s="4" t="inlineStr"/>
-      <c r="O42" s="4" t="inlineStr"/>
-      <c r="P42" s="4" t="inlineStr"/>
-      <c r="Q42" s="4" t="inlineStr"/>
-      <c r="R42" s="4" t="inlineStr"/>
-      <c r="S42" s="4" t="inlineStr"/>
-      <c r="T42" s="4" t="inlineStr"/>
+      <c r="A42" t="inlineStr"/>
+      <c r="B42" s="4" t="n"/>
+      <c r="C42" s="4" t="n"/>
+      <c r="D42" s="4" t="n"/>
+      <c r="E42" s="4" t="n"/>
+      <c r="F42" s="4" t="n"/>
+      <c r="G42" s="4" t="n"/>
+      <c r="H42" s="4" t="n"/>
+      <c r="I42" s="4" t="n"/>
+      <c r="J42" s="4" t="n"/>
+      <c r="K42" s="4" t="n"/>
+      <c r="L42" s="4" t="n"/>
+      <c r="M42" s="4" t="n"/>
+      <c r="N42" s="4" t="n"/>
+      <c r="O42" s="4" t="n"/>
+      <c r="P42" s="4" t="n"/>
+      <c r="Q42" s="4" t="n"/>
+      <c r="R42" s="4" t="n"/>
+      <c r="S42" s="4" t="n"/>
+      <c r="T42" s="4" t="n"/>
     </row>
     <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>Friday</t>
-        </is>
-      </c>
-      <c r="B43" s="4" t="inlineStr"/>
-      <c r="C43" s="17" t="inlineStr">
-        <is>
-          <t>CS262 (C202)</t>
-        </is>
-      </c>
-      <c r="D43" s="17" t="n"/>
-      <c r="E43" s="4" t="inlineStr"/>
-      <c r="F43" s="18" t="inlineStr">
-        <is>
-          <t>CS264 (C204)</t>
-        </is>
-      </c>
-      <c r="G43" s="18" t="n"/>
-      <c r="H43" s="18" t="n"/>
-      <c r="I43" s="4" t="inlineStr"/>
-      <c r="J43" s="4" t="inlineStr"/>
-      <c r="K43" s="4" t="inlineStr"/>
-      <c r="L43" s="4" t="inlineStr"/>
-      <c r="M43" s="4" t="inlineStr"/>
-      <c r="N43" s="4" t="inlineStr"/>
-      <c r="O43" s="4" t="inlineStr"/>
-      <c r="P43" s="4" t="inlineStr"/>
-      <c r="Q43" s="4" t="inlineStr"/>
-      <c r="R43" s="4" t="inlineStr"/>
-      <c r="S43" s="4" t="inlineStr"/>
-      <c r="T43" s="4" t="inlineStr"/>
+      <c r="A43" t="inlineStr"/>
+      <c r="B43" s="4" t="n"/>
+      <c r="C43" s="4" t="n"/>
+      <c r="D43" s="4" t="n"/>
+      <c r="E43" s="4" t="n"/>
+      <c r="F43" s="4" t="n"/>
+      <c r="G43" s="4" t="n"/>
+      <c r="H43" s="4" t="n"/>
+      <c r="I43" s="4" t="n"/>
+      <c r="J43" s="4" t="n"/>
+      <c r="K43" s="4" t="n"/>
+      <c r="L43" s="4" t="n"/>
+      <c r="M43" s="4" t="n"/>
+      <c r="N43" s="4" t="n"/>
+      <c r="O43" s="4" t="n"/>
+      <c r="P43" s="4" t="n"/>
+      <c r="Q43" s="4" t="n"/>
+      <c r="R43" s="4" t="n"/>
+      <c r="S43" s="4" t="n"/>
+      <c r="T43" s="4" t="n"/>
     </row>
     <row r="44">
-      <c r="A44" t="inlineStr"/>
+      <c r="A44" s="1" t="inlineStr">
+        <is>
+          <t>CSEB III Second Half</t>
+        </is>
+      </c>
       <c r="B44" s="4" t="n"/>
       <c r="C44" s="4" t="n"/>
       <c r="D44" s="4" t="n"/>
@@ -10075,192 +10023,220 @@
       <c r="T44" s="4" t="n"/>
     </row>
     <row r="45">
-      <c r="A45" t="inlineStr"/>
-      <c r="B45" s="4" t="n"/>
-      <c r="C45" s="4" t="n"/>
-      <c r="D45" s="4" t="n"/>
-      <c r="E45" s="4" t="n"/>
-      <c r="F45" s="4" t="n"/>
-      <c r="G45" s="4" t="n"/>
-      <c r="H45" s="4" t="n"/>
-      <c r="I45" s="4" t="n"/>
-      <c r="J45" s="4" t="n"/>
-      <c r="K45" s="4" t="n"/>
-      <c r="L45" s="4" t="n"/>
-      <c r="M45" s="4" t="n"/>
-      <c r="N45" s="4" t="n"/>
-      <c r="O45" s="4" t="n"/>
-      <c r="P45" s="4" t="n"/>
-      <c r="Q45" s="4" t="n"/>
-      <c r="R45" s="4" t="n"/>
-      <c r="S45" s="4" t="n"/>
-      <c r="T45" s="4" t="n"/>
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Day</t>
+        </is>
+      </c>
+      <c r="B45" s="3" t="inlineStr">
+        <is>
+          <t>07:30-09:00</t>
+        </is>
+      </c>
+      <c r="C45" s="3" t="inlineStr">
+        <is>
+          <t>09:00-10:00</t>
+        </is>
+      </c>
+      <c r="D45" s="3" t="inlineStr">
+        <is>
+          <t>10:00-10:30</t>
+        </is>
+      </c>
+      <c r="E45" s="3" t="inlineStr">
+        <is>
+          <t>10:30-10:45</t>
+        </is>
+      </c>
+      <c r="F45" s="3" t="inlineStr">
+        <is>
+          <t>10:45-11:00</t>
+        </is>
+      </c>
+      <c r="G45" s="3" t="inlineStr">
+        <is>
+          <t>11:00-12:00</t>
+        </is>
+      </c>
+      <c r="H45" s="3" t="inlineStr">
+        <is>
+          <t>12:00-12:15</t>
+        </is>
+      </c>
+      <c r="I45" s="3" t="inlineStr">
+        <is>
+          <t>12:15-12:30</t>
+        </is>
+      </c>
+      <c r="J45" s="3" t="inlineStr">
+        <is>
+          <t>12:30-12:45</t>
+        </is>
+      </c>
+      <c r="K45" s="3" t="inlineStr">
+        <is>
+          <t>12:45-13:15</t>
+        </is>
+      </c>
+      <c r="L45" s="3" t="inlineStr">
+        <is>
+          <t>13:15-14:00</t>
+        </is>
+      </c>
+      <c r="M45" s="3" t="inlineStr">
+        <is>
+          <t>14:00-14:30</t>
+        </is>
+      </c>
+      <c r="N45" s="3" t="inlineStr">
+        <is>
+          <t>14:30-15:30</t>
+        </is>
+      </c>
+      <c r="O45" s="3" t="inlineStr">
+        <is>
+          <t>15:30-15:40</t>
+        </is>
+      </c>
+      <c r="P45" s="3" t="inlineStr">
+        <is>
+          <t>15:40-16:00</t>
+        </is>
+      </c>
+      <c r="Q45" s="3" t="inlineStr">
+        <is>
+          <t>16:00-16:30</t>
+        </is>
+      </c>
+      <c r="R45" s="3" t="inlineStr">
+        <is>
+          <t>16:30-17:10</t>
+        </is>
+      </c>
+      <c r="S45" s="3" t="inlineStr">
+        <is>
+          <t>17:10-17:30</t>
+        </is>
+      </c>
+      <c r="T45" s="3" t="inlineStr">
+        <is>
+          <t>17:30-18:30</t>
+        </is>
+      </c>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="inlineStr">
-        <is>
-          <t>CSEB III Second Half</t>
-        </is>
-      </c>
-      <c r="B46" s="4" t="n"/>
-      <c r="C46" s="4" t="n"/>
-      <c r="D46" s="4" t="n"/>
-      <c r="E46" s="4" t="n"/>
-      <c r="F46" s="4" t="n"/>
-      <c r="G46" s="4" t="n"/>
-      <c r="H46" s="4" t="n"/>
-      <c r="I46" s="4" t="n"/>
-      <c r="J46" s="4" t="n"/>
-      <c r="K46" s="4" t="n"/>
-      <c r="L46" s="4" t="n"/>
-      <c r="M46" s="4" t="n"/>
-      <c r="N46" s="4" t="n"/>
-      <c r="O46" s="4" t="n"/>
-      <c r="P46" s="4" t="n"/>
-      <c r="Q46" s="4" t="n"/>
-      <c r="R46" s="4" t="n"/>
-      <c r="S46" s="4" t="n"/>
-      <c r="T46" s="4" t="n"/>
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Monday</t>
+        </is>
+      </c>
+      <c r="B46" s="4" t="inlineStr"/>
+      <c r="C46" s="5" t="inlineStr">
+        <is>
+          <t>Elective1</t>
+        </is>
+      </c>
+      <c r="D46" s="5" t="n"/>
+      <c r="E46" s="4" t="inlineStr"/>
+      <c r="F46" s="20" t="inlineStr">
+        <is>
+          <t>CS263 (C205)</t>
+        </is>
+      </c>
+      <c r="G46" s="20" t="n"/>
+      <c r="H46" s="20" t="n"/>
+      <c r="I46" s="18" t="inlineStr">
+        <is>
+          <t>CS264T (C203)</t>
+        </is>
+      </c>
+      <c r="J46" s="18" t="n"/>
+      <c r="K46" s="18" t="n"/>
+      <c r="L46" s="4" t="inlineStr"/>
+      <c r="M46" s="19" t="inlineStr">
+        <is>
+          <t>CS261 (C203)</t>
+        </is>
+      </c>
+      <c r="N46" s="19" t="n"/>
+      <c r="O46" s="4" t="inlineStr"/>
+      <c r="P46" s="4" t="inlineStr"/>
+      <c r="Q46" s="4" t="inlineStr"/>
+      <c r="R46" s="4" t="inlineStr"/>
+      <c r="S46" s="4" t="inlineStr"/>
+      <c r="T46" s="4" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Day</t>
-        </is>
-      </c>
-      <c r="B47" s="3" t="inlineStr">
-        <is>
-          <t>07:30-09:00</t>
-        </is>
-      </c>
-      <c r="C47" s="3" t="inlineStr">
-        <is>
-          <t>09:00-10:00</t>
-        </is>
-      </c>
-      <c r="D47" s="3" t="inlineStr">
-        <is>
-          <t>10:00-10:30</t>
-        </is>
-      </c>
-      <c r="E47" s="3" t="inlineStr">
-        <is>
-          <t>10:30-10:45</t>
-        </is>
-      </c>
-      <c r="F47" s="3" t="inlineStr">
-        <is>
-          <t>10:45-11:00</t>
-        </is>
-      </c>
-      <c r="G47" s="3" t="inlineStr">
-        <is>
-          <t>11:00-12:00</t>
-        </is>
-      </c>
-      <c r="H47" s="3" t="inlineStr">
-        <is>
-          <t>12:00-12:15</t>
-        </is>
-      </c>
-      <c r="I47" s="3" t="inlineStr">
-        <is>
-          <t>12:15-12:30</t>
-        </is>
-      </c>
-      <c r="J47" s="3" t="inlineStr">
-        <is>
-          <t>12:30-12:45</t>
-        </is>
-      </c>
-      <c r="K47" s="3" t="inlineStr">
-        <is>
-          <t>12:45-13:15</t>
-        </is>
-      </c>
-      <c r="L47" s="3" t="inlineStr">
-        <is>
-          <t>13:15-14:00</t>
-        </is>
-      </c>
-      <c r="M47" s="3" t="inlineStr">
-        <is>
-          <t>14:00-14:30</t>
-        </is>
-      </c>
-      <c r="N47" s="3" t="inlineStr">
-        <is>
-          <t>14:30-15:30</t>
-        </is>
-      </c>
-      <c r="O47" s="3" t="inlineStr">
-        <is>
-          <t>15:30-15:40</t>
-        </is>
-      </c>
-      <c r="P47" s="3" t="inlineStr">
-        <is>
-          <t>15:40-16:00</t>
-        </is>
-      </c>
-      <c r="Q47" s="3" t="inlineStr">
-        <is>
-          <t>16:00-16:30</t>
-        </is>
-      </c>
-      <c r="R47" s="3" t="inlineStr">
-        <is>
-          <t>16:30-17:10</t>
-        </is>
-      </c>
-      <c r="S47" s="3" t="inlineStr">
-        <is>
-          <t>17:10-17:30</t>
-        </is>
-      </c>
-      <c r="T47" s="3" t="inlineStr">
-        <is>
-          <t>17:30-18:30</t>
-        </is>
-      </c>
+          <t>Tuesday</t>
+        </is>
+      </c>
+      <c r="B47" s="4" t="inlineStr"/>
+      <c r="C47" s="5" t="inlineStr">
+        <is>
+          <t>Elective1</t>
+        </is>
+      </c>
+      <c r="D47" s="5" t="n"/>
+      <c r="E47" s="4" t="inlineStr"/>
+      <c r="F47" s="19" t="inlineStr">
+        <is>
+          <t>CS261T (C205)</t>
+        </is>
+      </c>
+      <c r="G47" s="19" t="n"/>
+      <c r="H47" s="4" t="inlineStr"/>
+      <c r="I47" s="4" t="inlineStr"/>
+      <c r="J47" s="4" t="inlineStr"/>
+      <c r="K47" s="4" t="inlineStr"/>
+      <c r="L47" s="4" t="inlineStr"/>
+      <c r="M47" s="20" t="inlineStr">
+        <is>
+          <t>CS263 (C205)</t>
+        </is>
+      </c>
+      <c r="N47" s="20" t="n"/>
+      <c r="O47" s="4" t="inlineStr"/>
+      <c r="P47" s="4" t="inlineStr"/>
+      <c r="Q47" s="4" t="inlineStr"/>
+      <c r="R47" s="4" t="inlineStr"/>
+      <c r="S47" s="4" t="inlineStr"/>
+      <c r="T47" s="4" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Monday</t>
+          <t>Wednesday</t>
         </is>
       </c>
       <c r="B48" s="4" t="inlineStr"/>
       <c r="C48" s="5" t="inlineStr">
         <is>
-          <t>Elective1</t>
-        </is>
-      </c>
-      <c r="D48" s="5" t="n"/>
+          <t>Elective1T</t>
+        </is>
+      </c>
+      <c r="D48" s="4" t="inlineStr"/>
       <c r="E48" s="4" t="inlineStr"/>
-      <c r="F48" s="20" t="inlineStr">
-        <is>
-          <t>CS263 (C205)</t>
-        </is>
-      </c>
-      <c r="G48" s="20" t="n"/>
-      <c r="H48" s="20" t="n"/>
-      <c r="I48" s="18" t="inlineStr">
-        <is>
-          <t>CS264T (C203)</t>
-        </is>
-      </c>
-      <c r="J48" s="18" t="n"/>
-      <c r="K48" s="18" t="n"/>
+      <c r="F48" s="17" t="inlineStr">
+        <is>
+          <t>CS262 (C205)</t>
+        </is>
+      </c>
+      <c r="G48" s="17" t="n"/>
+      <c r="H48" s="17" t="n"/>
+      <c r="I48" s="4" t="inlineStr"/>
+      <c r="J48" s="4" t="inlineStr"/>
+      <c r="K48" s="4" t="inlineStr"/>
       <c r="L48" s="4" t="inlineStr"/>
-      <c r="M48" s="19" t="inlineStr">
-        <is>
-          <t>CS261 (C203)</t>
-        </is>
-      </c>
-      <c r="N48" s="19" t="n"/>
-      <c r="O48" s="4" t="inlineStr"/>
-      <c r="P48" s="4" t="inlineStr"/>
+      <c r="M48" s="20" t="inlineStr">
+        <is>
+          <t>CS263 (Lab-L208)</t>
+        </is>
+      </c>
+      <c r="N48" s="20" t="n"/>
+      <c r="O48" s="20" t="n"/>
+      <c r="P48" s="20" t="n"/>
       <c r="Q48" s="4" t="inlineStr"/>
       <c r="R48" s="4" t="inlineStr"/>
       <c r="S48" s="4" t="inlineStr"/>
@@ -10269,34 +10245,30 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Tuesday</t>
+          <t>Thursday</t>
         </is>
       </c>
       <c r="B49" s="4" t="inlineStr"/>
-      <c r="C49" s="5" t="inlineStr">
-        <is>
-          <t>Elective1</t>
-        </is>
-      </c>
-      <c r="D49" s="5" t="n"/>
+      <c r="C49" s="17" t="inlineStr">
+        <is>
+          <t>CS262 (C205)</t>
+        </is>
+      </c>
+      <c r="D49" s="17" t="n"/>
       <c r="E49" s="4" t="inlineStr"/>
-      <c r="F49" s="19" t="inlineStr">
-        <is>
-          <t>CS261T (C205)</t>
-        </is>
-      </c>
-      <c r="G49" s="19" t="n"/>
-      <c r="H49" s="4" t="inlineStr"/>
+      <c r="F49" s="18" t="inlineStr">
+        <is>
+          <t>CS264 (C202)</t>
+        </is>
+      </c>
+      <c r="G49" s="18" t="n"/>
+      <c r="H49" s="18" t="n"/>
       <c r="I49" s="4" t="inlineStr"/>
       <c r="J49" s="4" t="inlineStr"/>
       <c r="K49" s="4" t="inlineStr"/>
       <c r="L49" s="4" t="inlineStr"/>
-      <c r="M49" s="20" t="inlineStr">
-        <is>
-          <t>CS263 (C205)</t>
-        </is>
-      </c>
-      <c r="N49" s="20" t="n"/>
+      <c r="M49" s="4" t="inlineStr"/>
+      <c r="N49" s="4" t="inlineStr"/>
       <c r="O49" s="4" t="inlineStr"/>
       <c r="P49" s="4" t="inlineStr"/>
       <c r="Q49" s="4" t="inlineStr"/>
@@ -10307,112 +10279,84 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Wednesday</t>
+          <t>Friday</t>
         </is>
       </c>
       <c r="B50" s="4" t="inlineStr"/>
-      <c r="C50" s="5" t="inlineStr">
-        <is>
-          <t>Elective1T</t>
-        </is>
-      </c>
-      <c r="D50" s="4" t="inlineStr"/>
+      <c r="C50" s="19" t="inlineStr">
+        <is>
+          <t>CS261 (C203)</t>
+        </is>
+      </c>
+      <c r="D50" s="19" t="n"/>
       <c r="E50" s="4" t="inlineStr"/>
       <c r="F50" s="17" t="inlineStr">
         <is>
-          <t>CS262 (C205)</t>
+          <t>CS262 (Lab-L208)</t>
         </is>
       </c>
       <c r="G50" s="17" t="n"/>
       <c r="H50" s="17" t="n"/>
-      <c r="I50" s="4" t="inlineStr"/>
-      <c r="J50" s="4" t="inlineStr"/>
+      <c r="I50" s="17" t="n"/>
+      <c r="J50" s="17" t="n"/>
       <c r="K50" s="4" t="inlineStr"/>
       <c r="L50" s="4" t="inlineStr"/>
-      <c r="M50" s="20" t="inlineStr">
-        <is>
-          <t>CS263 (Lab-L208)</t>
-        </is>
-      </c>
-      <c r="N50" s="20" t="n"/>
-      <c r="O50" s="20" t="n"/>
-      <c r="P50" s="20" t="n"/>
+      <c r="M50" s="18" t="inlineStr">
+        <is>
+          <t>CS264 (C202)</t>
+        </is>
+      </c>
+      <c r="N50" s="18" t="n"/>
+      <c r="O50" s="4" t="inlineStr"/>
+      <c r="P50" s="4" t="inlineStr"/>
       <c r="Q50" s="4" t="inlineStr"/>
       <c r="R50" s="4" t="inlineStr"/>
       <c r="S50" s="4" t="inlineStr"/>
       <c r="T50" s="4" t="inlineStr"/>
     </row>
     <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>Thursday</t>
-        </is>
-      </c>
-      <c r="B51" s="4" t="inlineStr"/>
-      <c r="C51" s="17" t="inlineStr">
-        <is>
-          <t>CS262 (C205)</t>
-        </is>
-      </c>
-      <c r="D51" s="17" t="n"/>
-      <c r="E51" s="4" t="inlineStr"/>
-      <c r="F51" s="18" t="inlineStr">
-        <is>
-          <t>CS264 (C202)</t>
-        </is>
-      </c>
-      <c r="G51" s="18" t="n"/>
-      <c r="H51" s="18" t="n"/>
-      <c r="I51" s="4" t="inlineStr"/>
-      <c r="J51" s="4" t="inlineStr"/>
-      <c r="K51" s="4" t="inlineStr"/>
-      <c r="L51" s="4" t="inlineStr"/>
-      <c r="M51" s="4" t="inlineStr"/>
-      <c r="N51" s="4" t="inlineStr"/>
-      <c r="O51" s="4" t="inlineStr"/>
-      <c r="P51" s="4" t="inlineStr"/>
-      <c r="Q51" s="4" t="inlineStr"/>
-      <c r="R51" s="4" t="inlineStr"/>
-      <c r="S51" s="4" t="inlineStr"/>
-      <c r="T51" s="4" t="inlineStr"/>
+      <c r="A51" t="inlineStr"/>
+      <c r="B51" s="4" t="n"/>
+      <c r="C51" s="4" t="n"/>
+      <c r="D51" s="4" t="n"/>
+      <c r="E51" s="4" t="n"/>
+      <c r="F51" s="4" t="n"/>
+      <c r="G51" s="4" t="n"/>
+      <c r="H51" s="4" t="n"/>
+      <c r="I51" s="4" t="n"/>
+      <c r="J51" s="4" t="n"/>
+      <c r="K51" s="4" t="n"/>
+      <c r="L51" s="4" t="n"/>
+      <c r="M51" s="4" t="n"/>
+      <c r="N51" s="4" t="n"/>
+      <c r="O51" s="4" t="n"/>
+      <c r="P51" s="4" t="n"/>
+      <c r="Q51" s="4" t="n"/>
+      <c r="R51" s="4" t="n"/>
+      <c r="S51" s="4" t="n"/>
+      <c r="T51" s="4" t="n"/>
     </row>
     <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>Friday</t>
-        </is>
-      </c>
-      <c r="B52" s="4" t="inlineStr"/>
-      <c r="C52" s="19" t="inlineStr">
-        <is>
-          <t>CS261 (C203)</t>
-        </is>
-      </c>
-      <c r="D52" s="19" t="n"/>
-      <c r="E52" s="4" t="inlineStr"/>
-      <c r="F52" s="17" t="inlineStr">
-        <is>
-          <t>CS262 (Lab-L208)</t>
-        </is>
-      </c>
-      <c r="G52" s="17" t="n"/>
-      <c r="H52" s="17" t="n"/>
-      <c r="I52" s="17" t="n"/>
-      <c r="J52" s="17" t="n"/>
-      <c r="K52" s="4" t="inlineStr"/>
-      <c r="L52" s="4" t="inlineStr"/>
-      <c r="M52" s="18" t="inlineStr">
-        <is>
-          <t>CS264 (C202)</t>
-        </is>
-      </c>
-      <c r="N52" s="18" t="n"/>
-      <c r="O52" s="4" t="inlineStr"/>
-      <c r="P52" s="4" t="inlineStr"/>
-      <c r="Q52" s="4" t="inlineStr"/>
-      <c r="R52" s="4" t="inlineStr"/>
-      <c r="S52" s="4" t="inlineStr"/>
-      <c r="T52" s="4" t="inlineStr"/>
+      <c r="A52" t="inlineStr"/>
+      <c r="B52" s="4" t="n"/>
+      <c r="C52" s="4" t="n"/>
+      <c r="D52" s="4" t="n"/>
+      <c r="E52" s="4" t="n"/>
+      <c r="F52" s="4" t="n"/>
+      <c r="G52" s="4" t="n"/>
+      <c r="H52" s="4" t="n"/>
+      <c r="I52" s="4" t="n"/>
+      <c r="J52" s="4" t="n"/>
+      <c r="K52" s="4" t="n"/>
+      <c r="L52" s="4" t="n"/>
+      <c r="M52" s="4" t="n"/>
+      <c r="N52" s="4" t="n"/>
+      <c r="O52" s="4" t="n"/>
+      <c r="P52" s="4" t="n"/>
+      <c r="Q52" s="4" t="n"/>
+      <c r="R52" s="4" t="n"/>
+      <c r="S52" s="4" t="n"/>
+      <c r="T52" s="4" t="n"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr"/>
@@ -10437,7 +10381,11 @@
       <c r="T53" s="4" t="n"/>
     </row>
     <row r="54">
-      <c r="A54" t="inlineStr"/>
+      <c r="A54" s="12" t="inlineStr">
+        <is>
+          <t>Legend - CSEB III</t>
+        </is>
+      </c>
       <c r="B54" s="4" t="n"/>
       <c r="C54" s="4" t="n"/>
       <c r="D54" s="4" t="n"/>
@@ -10459,14 +10407,46 @@
       <c r="T54" s="4" t="n"/>
     </row>
     <row r="55">
-      <c r="A55" t="inlineStr"/>
-      <c r="B55" s="4" t="n"/>
-      <c r="C55" s="4" t="n"/>
-      <c r="D55" s="4" t="n"/>
-      <c r="E55" s="4" t="n"/>
-      <c r="F55" s="4" t="n"/>
-      <c r="G55" s="4" t="n"/>
-      <c r="H55" s="4" t="n"/>
+      <c r="A55" s="13" t="inlineStr">
+        <is>
+          <t>Course Code</t>
+        </is>
+      </c>
+      <c r="B55" s="14" t="inlineStr">
+        <is>
+          <t>Course Title</t>
+        </is>
+      </c>
+      <c r="C55" s="14" t="inlineStr">
+        <is>
+          <t>L-T-P-S-C</t>
+        </is>
+      </c>
+      <c r="D55" s="14" t="inlineStr">
+        <is>
+          <t>Faculty</t>
+        </is>
+      </c>
+      <c r="E55" s="14" t="inlineStr">
+        <is>
+          <t>Semester Half</t>
+        </is>
+      </c>
+      <c r="F55" s="15" t="inlineStr">
+        <is>
+          <t>Elective</t>
+        </is>
+      </c>
+      <c r="G55" s="15" t="inlineStr">
+        <is>
+          <t>Elective Basket</t>
+        </is>
+      </c>
+      <c r="H55" s="15" t="inlineStr">
+        <is>
+          <t>Elective Room</t>
+        </is>
+      </c>
       <c r="I55" s="4" t="n"/>
       <c r="J55" s="4" t="n"/>
       <c r="K55" s="4" t="n"/>
@@ -10481,18 +10461,42 @@
       <c r="T55" s="4" t="n"/>
     </row>
     <row r="56">
-      <c r="A56" s="12" t="inlineStr">
-        <is>
-          <t>Legend - CSEB III</t>
-        </is>
-      </c>
-      <c r="B56" s="4" t="n"/>
-      <c r="C56" s="4" t="n"/>
-      <c r="D56" s="4" t="n"/>
-      <c r="E56" s="4" t="n"/>
-      <c r="F56" s="4" t="n"/>
-      <c r="G56" s="4" t="n"/>
-      <c r="H56" s="4" t="n"/>
+      <c r="A56" s="16" t="inlineStr">
+        <is>
+          <t>CS261</t>
+        </is>
+      </c>
+      <c r="B56" s="3" t="inlineStr">
+        <is>
+          <t>Operating Systems</t>
+        </is>
+      </c>
+      <c r="C56" s="3" t="inlineStr">
+        <is>
+          <t>3-1-0-4-2</t>
+        </is>
+      </c>
+      <c r="D56" s="3" t="inlineStr">
+        <is>
+          <t>Dr. Suvadip Hazra</t>
+        </is>
+      </c>
+      <c r="E56" s="3" t="inlineStr">
+        <is>
+          <t>Second Half</t>
+        </is>
+      </c>
+      <c r="F56" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G56" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H56" s="4" t="inlineStr"/>
       <c r="I56" s="4" t="n"/>
       <c r="J56" s="4" t="n"/>
       <c r="K56" s="4" t="n"/>
@@ -10507,46 +10511,42 @@
       <c r="T56" s="4" t="n"/>
     </row>
     <row r="57">
-      <c r="A57" s="13" t="inlineStr">
-        <is>
-          <t>Course Code</t>
-        </is>
-      </c>
-      <c r="B57" s="14" t="inlineStr">
-        <is>
-          <t>Course Title</t>
-        </is>
-      </c>
-      <c r="C57" s="14" t="inlineStr">
-        <is>
-          <t>L-T-P-S-C</t>
-        </is>
-      </c>
-      <c r="D57" s="14" t="inlineStr">
-        <is>
-          <t>Faculty</t>
-        </is>
-      </c>
-      <c r="E57" s="14" t="inlineStr">
-        <is>
-          <t>Semester Half</t>
-        </is>
-      </c>
-      <c r="F57" s="15" t="inlineStr">
-        <is>
-          <t>Elective</t>
-        </is>
-      </c>
-      <c r="G57" s="15" t="inlineStr">
-        <is>
-          <t>Elective Basket</t>
-        </is>
-      </c>
-      <c r="H57" s="15" t="inlineStr">
-        <is>
-          <t>Elective Room</t>
-        </is>
-      </c>
+      <c r="A57" s="16" t="inlineStr">
+        <is>
+          <t>CS262</t>
+        </is>
+      </c>
+      <c r="B57" s="3" t="inlineStr">
+        <is>
+          <t>Software design tools and technique</t>
+        </is>
+      </c>
+      <c r="C57" s="3" t="inlineStr">
+        <is>
+          <t>3-0-2-0-3</t>
+        </is>
+      </c>
+      <c r="D57" s="3" t="inlineStr">
+        <is>
+          <t>Dr. Vivekraj V K</t>
+        </is>
+      </c>
+      <c r="E57" s="3" t="inlineStr">
+        <is>
+          <t>Full Sem</t>
+        </is>
+      </c>
+      <c r="F57" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G57" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H57" s="4" t="inlineStr"/>
       <c r="I57" s="4" t="n"/>
       <c r="J57" s="4" t="n"/>
       <c r="K57" s="4" t="n"/>
@@ -10563,27 +10563,27 @@
     <row r="58">
       <c r="A58" s="16" t="inlineStr">
         <is>
-          <t>MA261</t>
+          <t>CS263</t>
         </is>
       </c>
       <c r="B58" s="3" t="inlineStr">
         <is>
-          <t>Differential Equations</t>
+          <t>Design &amp; Analysis of Algorithms</t>
         </is>
       </c>
       <c r="C58" s="3" t="inlineStr">
         <is>
-          <t>3-1-0-0-2</t>
+          <t>3-0-2-0-4</t>
         </is>
       </c>
       <c r="D58" s="3" t="inlineStr">
         <is>
-          <t>Dr. Anand Barangi</t>
+          <t>Dr. Pramod Yelmewad</t>
         </is>
       </c>
       <c r="E58" s="3" t="inlineStr">
         <is>
-          <t>First Half</t>
+          <t>Full Sem</t>
         </is>
       </c>
       <c r="F58" s="3" t="inlineStr">
@@ -10613,27 +10613,27 @@
     <row r="59">
       <c r="A59" s="16" t="inlineStr">
         <is>
-          <t>MA262</t>
+          <t>CS264</t>
         </is>
       </c>
       <c r="B59" s="3" t="inlineStr">
         <is>
-          <t>Multivariate Calculus</t>
+          <t>Computer Networks</t>
         </is>
       </c>
       <c r="C59" s="3" t="inlineStr">
         <is>
-          <t>3-1-0-0-2</t>
+          <t>3-1-0-0-4</t>
         </is>
       </c>
       <c r="D59" s="3" t="inlineStr">
         <is>
-          <t>Dr. Somen Bhattacharjee</t>
+          <t>Dr. Prabhu Prasad BM</t>
         </is>
       </c>
       <c r="E59" s="3" t="inlineStr">
         <is>
-          <t>Second Half</t>
+          <t>Full Sem</t>
         </is>
       </c>
       <c r="F59" s="3" t="inlineStr">
@@ -10663,40 +10663,44 @@
     <row r="60">
       <c r="A60" s="16" t="inlineStr">
         <is>
-          <t>CS261</t>
+          <t>EC251</t>
         </is>
       </c>
       <c r="B60" s="3" t="inlineStr">
         <is>
-          <t>Operating Systems</t>
+          <t>Electronics System Design-I</t>
         </is>
       </c>
       <c r="C60" s="3" t="inlineStr">
         <is>
-          <t>3-1-0-4-2</t>
+          <t>3-1-0-0-2</t>
         </is>
       </c>
       <c r="D60" s="3" t="inlineStr">
         <is>
-          <t>Dr. Suvadip Hazra</t>
+          <t>Dr. Pankaj Kumar</t>
         </is>
       </c>
       <c r="E60" s="3" t="inlineStr">
         <is>
-          <t>Second Half</t>
+          <t>First Half</t>
         </is>
       </c>
       <c r="F60" s="3" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G60" s="3" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H60" s="4" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H60" s="3" t="inlineStr">
+        <is>
+          <t>C301</t>
+        </is>
+      </c>
       <c r="I60" s="4" t="n"/>
       <c r="J60" s="4" t="n"/>
       <c r="K60" s="4" t="n"/>
@@ -10713,40 +10717,44 @@
     <row r="61">
       <c r="A61" s="16" t="inlineStr">
         <is>
-          <t>CS262</t>
+          <t>EC252</t>
         </is>
       </c>
       <c r="B61" s="3" t="inlineStr">
         <is>
-          <t>Software design tools and technique</t>
+          <t>Introduction of RFIC design</t>
         </is>
       </c>
       <c r="C61" s="3" t="inlineStr">
         <is>
-          <t>3-0-2-0-3</t>
+          <t>3-1-0-0-2</t>
         </is>
       </c>
       <c r="D61" s="3" t="inlineStr">
         <is>
-          <t>Dr. Vivekraj V K</t>
+          <t>Dr. Rajesh Kumar</t>
         </is>
       </c>
       <c r="E61" s="3" t="inlineStr">
         <is>
-          <t>Full Sem</t>
+          <t>Second Half</t>
         </is>
       </c>
       <c r="F61" s="3" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G61" s="3" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H61" s="4" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H61" s="3" t="inlineStr">
+        <is>
+          <t>C102</t>
+        </is>
+      </c>
       <c r="I61" s="4" t="n"/>
       <c r="J61" s="4" t="n"/>
       <c r="K61" s="4" t="n"/>
@@ -10763,40 +10771,44 @@
     <row r="62">
       <c r="A62" s="16" t="inlineStr">
         <is>
-          <t>CS263</t>
+          <t>EC253</t>
         </is>
       </c>
       <c r="B62" s="3" t="inlineStr">
         <is>
-          <t>Design &amp; Analysis of Algorithms</t>
+          <t>Introduction to Embedded Signal Intelligence</t>
         </is>
       </c>
       <c r="C62" s="3" t="inlineStr">
         <is>
-          <t>3-0-2-0-4</t>
+          <t>3-1-0-0-2</t>
         </is>
       </c>
       <c r="D62" s="3" t="inlineStr">
         <is>
-          <t>Dr. Pramod Yelmewad</t>
+          <t>Dr. Sibasankar Padhy</t>
         </is>
       </c>
       <c r="E62" s="3" t="inlineStr">
         <is>
-          <t>Full Sem</t>
+          <t>Second Half</t>
         </is>
       </c>
       <c r="F62" s="3" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G62" s="3" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H62" s="4" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H62" s="3" t="inlineStr">
+        <is>
+          <t>C401</t>
+        </is>
+      </c>
       <c r="I62" s="4" t="n"/>
       <c r="J62" s="4" t="n"/>
       <c r="K62" s="4" t="n"/>
@@ -10813,40 +10825,44 @@
     <row r="63">
       <c r="A63" s="16" t="inlineStr">
         <is>
-          <t>CS264</t>
+          <t>EC254</t>
         </is>
       </c>
       <c r="B63" s="3" t="inlineStr">
         <is>
-          <t>Computer Networks</t>
+          <t>Electronic Systems Engineering</t>
         </is>
       </c>
       <c r="C63" s="3" t="inlineStr">
         <is>
-          <t>3-1-0-0-4</t>
+          <t>3-1-0-0-2</t>
         </is>
       </c>
       <c r="D63" s="3" t="inlineStr">
         <is>
-          <t>Dr. Prabhu Prasad BM</t>
+          <t>Mr. Mallikarjun Kande</t>
         </is>
       </c>
       <c r="E63" s="3" t="inlineStr">
         <is>
-          <t>Full Sem</t>
+          <t>First Half</t>
         </is>
       </c>
       <c r="F63" s="3" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G63" s="3" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H63" s="4" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H63" s="3" t="inlineStr">
+        <is>
+          <t>C003</t>
+        </is>
+      </c>
       <c r="I63" s="4" t="n"/>
       <c r="J63" s="4" t="n"/>
       <c r="K63" s="4" t="n"/>
@@ -10863,12 +10879,12 @@
     <row r="64">
       <c r="A64" s="16" t="inlineStr">
         <is>
-          <t>EC251</t>
+          <t>CS152</t>
         </is>
       </c>
       <c r="B64" s="3" t="inlineStr">
         <is>
-          <t>Electronics System Design-I</t>
+          <t>Data Science with Python</t>
         </is>
       </c>
       <c r="C64" s="3" t="inlineStr">
@@ -10878,7 +10894,7 @@
       </c>
       <c r="D64" s="3" t="inlineStr">
         <is>
-          <t>Dr. Pankaj Kumar</t>
+          <t>Dr. Abdul Wahid</t>
         </is>
       </c>
       <c r="E64" s="3" t="inlineStr">
@@ -10898,7 +10914,7 @@
       </c>
       <c r="H64" s="3" t="inlineStr">
         <is>
-          <t>C301</t>
+          <t>C302</t>
         </is>
       </c>
       <c r="I64" s="4" t="n"/>
@@ -10917,12 +10933,12 @@
     <row r="65">
       <c r="A65" s="16" t="inlineStr">
         <is>
-          <t>EC252</t>
+          <t>CS251</t>
         </is>
       </c>
       <c r="B65" s="3" t="inlineStr">
         <is>
-          <t>Introduction of RFIC design</t>
+          <t>2D Computer Graphics</t>
         </is>
       </c>
       <c r="C65" s="3" t="inlineStr">
@@ -10932,12 +10948,12 @@
       </c>
       <c r="D65" s="3" t="inlineStr">
         <is>
-          <t>Dr. Rajesh Kumar</t>
+          <t>Dr. Vivekraj V K</t>
         </is>
       </c>
       <c r="E65" s="3" t="inlineStr">
         <is>
-          <t>Second Half</t>
+          <t>First Half</t>
         </is>
       </c>
       <c r="F65" s="3" t="inlineStr">
@@ -10952,7 +10968,7 @@
       </c>
       <c r="H65" s="3" t="inlineStr">
         <is>
-          <t>C102</t>
+          <t>C303</t>
         </is>
       </c>
       <c r="I65" s="4" t="n"/>
@@ -10969,46 +10985,14 @@
       <c r="T65" s="4" t="n"/>
     </row>
     <row r="66">
-      <c r="A66" s="16" t="inlineStr">
-        <is>
-          <t>EC253</t>
-        </is>
-      </c>
-      <c r="B66" s="3" t="inlineStr">
-        <is>
-          <t>Introduction to Embedded Signal Intelligence</t>
-        </is>
-      </c>
-      <c r="C66" s="3" t="inlineStr">
-        <is>
-          <t>3-1-0-0-2</t>
-        </is>
-      </c>
-      <c r="D66" s="3" t="inlineStr">
-        <is>
-          <t>Dr. Sibasankar Padhy</t>
-        </is>
-      </c>
-      <c r="E66" s="3" t="inlineStr">
-        <is>
-          <t>Second Half</t>
-        </is>
-      </c>
-      <c r="F66" s="3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G66" s="3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H66" s="3" t="inlineStr">
-        <is>
-          <t>C401</t>
-        </is>
-      </c>
+      <c r="A66" t="inlineStr"/>
+      <c r="B66" s="4" t="n"/>
+      <c r="C66" s="4" t="n"/>
+      <c r="D66" s="4" t="n"/>
+      <c r="E66" s="4" t="n"/>
+      <c r="F66" s="4" t="n"/>
+      <c r="G66" s="4" t="n"/>
+      <c r="H66" s="4" t="n"/>
       <c r="I66" s="4" t="n"/>
       <c r="J66" s="4" t="n"/>
       <c r="K66" s="4" t="n"/>
@@ -11022,241 +11006,57 @@
       <c r="S66" s="4" t="n"/>
       <c r="T66" s="4" t="n"/>
     </row>
-    <row r="67">
-      <c r="A67" s="16" t="inlineStr">
-        <is>
-          <t>EC254</t>
-        </is>
-      </c>
-      <c r="B67" s="3" t="inlineStr">
-        <is>
-          <t>Electronic Systems Engineering</t>
-        </is>
-      </c>
-      <c r="C67" s="3" t="inlineStr">
-        <is>
-          <t>3-1-0-0-2</t>
-        </is>
-      </c>
-      <c r="D67" s="3" t="inlineStr">
-        <is>
-          <t>Mr. Mallikarjun Kande</t>
-        </is>
-      </c>
-      <c r="E67" s="3" t="inlineStr">
-        <is>
-          <t>First Half</t>
-        </is>
-      </c>
-      <c r="F67" s="3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G67" s="3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H67" s="3" t="inlineStr">
-        <is>
-          <t>C003</t>
-        </is>
-      </c>
-      <c r="I67" s="4" t="n"/>
-      <c r="J67" s="4" t="n"/>
-      <c r="K67" s="4" t="n"/>
-      <c r="L67" s="4" t="n"/>
-      <c r="M67" s="4" t="n"/>
-      <c r="N67" s="4" t="n"/>
-      <c r="O67" s="4" t="n"/>
-      <c r="P67" s="4" t="n"/>
-      <c r="Q67" s="4" t="n"/>
-      <c r="R67" s="4" t="n"/>
-      <c r="S67" s="4" t="n"/>
-      <c r="T67" s="4" t="n"/>
-    </row>
-    <row r="68">
-      <c r="A68" s="16" t="inlineStr">
-        <is>
-          <t>CS152</t>
-        </is>
-      </c>
-      <c r="B68" s="3" t="inlineStr">
-        <is>
-          <t>Data Science with Python</t>
-        </is>
-      </c>
-      <c r="C68" s="3" t="inlineStr">
-        <is>
-          <t>3-1-0-0-2</t>
-        </is>
-      </c>
-      <c r="D68" s="3" t="inlineStr">
-        <is>
-          <t>Dr. Abdul Wahid</t>
-        </is>
-      </c>
-      <c r="E68" s="3" t="inlineStr">
-        <is>
-          <t>First Half</t>
-        </is>
-      </c>
-      <c r="F68" s="3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G68" s="3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H68" s="3" t="inlineStr">
-        <is>
-          <t>C302</t>
-        </is>
-      </c>
-      <c r="I68" s="4" t="n"/>
-      <c r="J68" s="4" t="n"/>
-      <c r="K68" s="4" t="n"/>
-      <c r="L68" s="4" t="n"/>
-      <c r="M68" s="4" t="n"/>
-      <c r="N68" s="4" t="n"/>
-      <c r="O68" s="4" t="n"/>
-      <c r="P68" s="4" t="n"/>
-      <c r="Q68" s="4" t="n"/>
-      <c r="R68" s="4" t="n"/>
-      <c r="S68" s="4" t="n"/>
-      <c r="T68" s="4" t="n"/>
-    </row>
-    <row r="69">
-      <c r="A69" s="16" t="inlineStr">
-        <is>
-          <t>CS251</t>
-        </is>
-      </c>
-      <c r="B69" s="3" t="inlineStr">
-        <is>
-          <t>2D Computer Graphics</t>
-        </is>
-      </c>
-      <c r="C69" s="3" t="inlineStr">
-        <is>
-          <t>3-1-0-0-2</t>
-        </is>
-      </c>
-      <c r="D69" s="3" t="inlineStr">
-        <is>
-          <t>Dr. Vivekraj V K</t>
-        </is>
-      </c>
-      <c r="E69" s="3" t="inlineStr">
-        <is>
-          <t>First Half</t>
-        </is>
-      </c>
-      <c r="F69" s="3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G69" s="3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H69" s="3" t="inlineStr">
-        <is>
-          <t>C303</t>
-        </is>
-      </c>
-      <c r="I69" s="4" t="n"/>
-      <c r="J69" s="4" t="n"/>
-      <c r="K69" s="4" t="n"/>
-      <c r="L69" s="4" t="n"/>
-      <c r="M69" s="4" t="n"/>
-      <c r="N69" s="4" t="n"/>
-      <c r="O69" s="4" t="n"/>
-      <c r="P69" s="4" t="n"/>
-      <c r="Q69" s="4" t="n"/>
-      <c r="R69" s="4" t="n"/>
-      <c r="S69" s="4" t="n"/>
-      <c r="T69" s="4" t="n"/>
-    </row>
-    <row r="70">
-      <c r="A70" t="inlineStr"/>
-      <c r="B70" s="4" t="n"/>
-      <c r="C70" s="4" t="n"/>
-      <c r="D70" s="4" t="n"/>
-      <c r="E70" s="4" t="n"/>
-      <c r="F70" s="4" t="n"/>
-      <c r="G70" s="4" t="n"/>
-      <c r="H70" s="4" t="n"/>
-      <c r="I70" s="4" t="n"/>
-      <c r="J70" s="4" t="n"/>
-      <c r="K70" s="4" t="n"/>
-      <c r="L70" s="4" t="n"/>
-      <c r="M70" s="4" t="n"/>
-      <c r="N70" s="4" t="n"/>
-      <c r="O70" s="4" t="n"/>
-      <c r="P70" s="4" t="n"/>
-      <c r="Q70" s="4" t="n"/>
-      <c r="R70" s="4" t="n"/>
-      <c r="S70" s="4" t="n"/>
-      <c r="T70" s="4" t="n"/>
-    </row>
   </sheetData>
   <mergeCells count="49">
     <mergeCell ref="Q5:S5"/>
     <mergeCell ref="F5:H5"/>
     <mergeCell ref="F41:H41"/>
     <mergeCell ref="C5:D5"/>
-    <mergeCell ref="C42:D42"/>
-    <mergeCell ref="F50:H50"/>
     <mergeCell ref="C14:D14"/>
-    <mergeCell ref="M52:N52"/>
-    <mergeCell ref="M49:N49"/>
-    <mergeCell ref="M39:N39"/>
-    <mergeCell ref="M48:N48"/>
+    <mergeCell ref="F40:J40"/>
     <mergeCell ref="C4:D4"/>
-    <mergeCell ref="M50:P50"/>
+    <mergeCell ref="F38:H38"/>
+    <mergeCell ref="F46:H46"/>
+    <mergeCell ref="C47:D47"/>
     <mergeCell ref="C16:D16"/>
     <mergeCell ref="F13:H13"/>
-    <mergeCell ref="F42:J42"/>
-    <mergeCell ref="F43:H43"/>
-    <mergeCell ref="I48:K48"/>
+    <mergeCell ref="C41:D41"/>
+    <mergeCell ref="C50:D50"/>
     <mergeCell ref="C40:D40"/>
     <mergeCell ref="F48:H48"/>
+    <mergeCell ref="F39:H39"/>
     <mergeCell ref="F8:J8"/>
+    <mergeCell ref="F50:J50"/>
     <mergeCell ref="M5:P5"/>
     <mergeCell ref="F17:J17"/>
-    <mergeCell ref="C43:D43"/>
+    <mergeCell ref="I38:K38"/>
+    <mergeCell ref="C46:D46"/>
+    <mergeCell ref="F47:G47"/>
     <mergeCell ref="F14:H14"/>
     <mergeCell ref="M6:N6"/>
     <mergeCell ref="I13:K13"/>
-    <mergeCell ref="C51:D51"/>
+    <mergeCell ref="M48:P48"/>
+    <mergeCell ref="M37:N37"/>
+    <mergeCell ref="M46:N46"/>
+    <mergeCell ref="F49:H49"/>
     <mergeCell ref="F4:H4"/>
-    <mergeCell ref="I40:K40"/>
-    <mergeCell ref="C52:D52"/>
-    <mergeCell ref="C48:D48"/>
-    <mergeCell ref="C39:D39"/>
     <mergeCell ref="C8:D8"/>
     <mergeCell ref="I6:K6"/>
     <mergeCell ref="M17:N17"/>
-    <mergeCell ref="F52:J52"/>
     <mergeCell ref="F16:H16"/>
+    <mergeCell ref="I46:K46"/>
     <mergeCell ref="F6:H6"/>
-    <mergeCell ref="F39:J39"/>
-    <mergeCell ref="F49:G49"/>
-    <mergeCell ref="F40:H40"/>
+    <mergeCell ref="F37:J37"/>
+    <mergeCell ref="C38:D38"/>
+    <mergeCell ref="M47:N47"/>
+    <mergeCell ref="C37:D37"/>
     <mergeCell ref="M15:P15"/>
+    <mergeCell ref="M50:N50"/>
     <mergeCell ref="C13:D13"/>
     <mergeCell ref="F7:H7"/>
     <mergeCell ref="F15:H15"/>
     <mergeCell ref="M4:N4"/>
     <mergeCell ref="C49:D49"/>
-    <mergeCell ref="F51:H51"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Balanced_Timetable_latest.xlsx
+++ b/Balanced_Timetable_latest.xlsx
@@ -10246,10 +10246,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T34"/>
+  <dimension ref="A1:T38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="21" customWidth="1" min="1" max="1"/>
+    <col width="58" customWidth="1" min="1" max="1"/>
     <col width="43" customWidth="1" min="2" max="2"/>
     <col width="15" customWidth="1" min="3" max="3"/>
     <col width="28" customWidth="1" min="4" max="4"/>
@@ -10589,7 +10589,11 @@
       <c r="T8" s="4" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr"/>
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>WARNING: Courses missing from generated timetable output</t>
+        </is>
+      </c>
       <c r="B9" s="4" t="n"/>
       <c r="C9" s="4" t="n"/>
       <c r="D9" s="4" t="n"/>
@@ -10611,7 +10615,11 @@
       <c r="T9" s="4" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr"/>
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>DS308: combined-course constraints prevented placement</t>
+        </is>
+      </c>
       <c r="B10" s="4" t="n"/>
       <c r="C10" s="4" t="n"/>
       <c r="D10" s="4" t="n"/>
@@ -10633,11 +10641,7 @@
       <c r="T10" s="4" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="inlineStr">
-        <is>
-          <t>DSAI-IV Second Half</t>
-        </is>
-      </c>
+      <c r="A11" t="inlineStr"/>
       <c r="B11" s="4" t="n"/>
       <c r="C11" s="4" t="n"/>
       <c r="D11" s="4" t="n"/>
@@ -10659,214 +10663,186 @@
       <c r="T11" s="4" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Day</t>
-        </is>
-      </c>
-      <c r="B12" s="3" t="inlineStr">
-        <is>
-          <t>07:30-09:00</t>
-        </is>
-      </c>
-      <c r="C12" s="3" t="inlineStr">
-        <is>
-          <t>09:00-10:00</t>
-        </is>
-      </c>
-      <c r="D12" s="3" t="inlineStr">
-        <is>
-          <t>10:00-10:30</t>
-        </is>
-      </c>
-      <c r="E12" s="3" t="inlineStr">
-        <is>
-          <t>10:30-10:45</t>
-        </is>
-      </c>
-      <c r="F12" s="3" t="inlineStr">
-        <is>
-          <t>10:45-11:00</t>
-        </is>
-      </c>
-      <c r="G12" s="3" t="inlineStr">
-        <is>
-          <t>11:00-12:00</t>
-        </is>
-      </c>
-      <c r="H12" s="3" t="inlineStr">
-        <is>
-          <t>12:00-12:15</t>
-        </is>
-      </c>
-      <c r="I12" s="3" t="inlineStr">
-        <is>
-          <t>12:15-12:30</t>
-        </is>
-      </c>
-      <c r="J12" s="3" t="inlineStr">
-        <is>
-          <t>12:30-12:45</t>
-        </is>
-      </c>
-      <c r="K12" s="3" t="inlineStr">
-        <is>
-          <t>12:45-13:15</t>
-        </is>
-      </c>
-      <c r="L12" s="3" t="inlineStr">
-        <is>
-          <t>13:15-14:00</t>
-        </is>
-      </c>
-      <c r="M12" s="3" t="inlineStr">
-        <is>
-          <t>14:00-14:30</t>
-        </is>
-      </c>
-      <c r="N12" s="3" t="inlineStr">
-        <is>
-          <t>14:30-15:30</t>
-        </is>
-      </c>
-      <c r="O12" s="3" t="inlineStr">
-        <is>
-          <t>15:30-15:40</t>
-        </is>
-      </c>
-      <c r="P12" s="3" t="inlineStr">
-        <is>
-          <t>15:40-16:00</t>
-        </is>
-      </c>
-      <c r="Q12" s="3" t="inlineStr">
-        <is>
-          <t>16:00-16:30</t>
-        </is>
-      </c>
-      <c r="R12" s="3" t="inlineStr">
-        <is>
-          <t>16:30-17:10</t>
-        </is>
-      </c>
-      <c r="S12" s="3" t="inlineStr">
-        <is>
-          <t>17:10-17:30</t>
-        </is>
-      </c>
-      <c r="T12" s="3" t="inlineStr">
-        <is>
-          <t>17:30-18:30</t>
-        </is>
-      </c>
+      <c r="A12" t="inlineStr"/>
+      <c r="B12" s="4" t="n"/>
+      <c r="C12" s="4" t="n"/>
+      <c r="D12" s="4" t="n"/>
+      <c r="E12" s="4" t="n"/>
+      <c r="F12" s="4" t="n"/>
+      <c r="G12" s="4" t="n"/>
+      <c r="H12" s="4" t="n"/>
+      <c r="I12" s="4" t="n"/>
+      <c r="J12" s="4" t="n"/>
+      <c r="K12" s="4" t="n"/>
+      <c r="L12" s="4" t="n"/>
+      <c r="M12" s="4" t="n"/>
+      <c r="N12" s="4" t="n"/>
+      <c r="O12" s="4" t="n"/>
+      <c r="P12" s="4" t="n"/>
+      <c r="Q12" s="4" t="n"/>
+      <c r="R12" s="4" t="n"/>
+      <c r="S12" s="4" t="n"/>
+      <c r="T12" s="4" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Monday</t>
-        </is>
-      </c>
-      <c r="B13" s="4" t="inlineStr"/>
-      <c r="C13" s="11" t="inlineStr">
-        <is>
-          <t>Elective2</t>
-        </is>
-      </c>
-      <c r="D13" s="11" t="n"/>
-      <c r="E13" s="4" t="inlineStr"/>
-      <c r="F13" s="29" t="inlineStr">
-        <is>
-          <t>DA263T (C403)</t>
-        </is>
-      </c>
-      <c r="G13" s="29" t="n"/>
-      <c r="H13" s="4" t="inlineStr"/>
-      <c r="I13" s="4" t="inlineStr"/>
-      <c r="J13" s="4" t="inlineStr"/>
-      <c r="K13" s="4" t="inlineStr"/>
-      <c r="L13" s="4" t="inlineStr"/>
-      <c r="M13" s="28" t="inlineStr">
-        <is>
-          <t>DA265 (C405)</t>
-        </is>
-      </c>
-      <c r="N13" s="28" t="n"/>
-      <c r="O13" s="4" t="inlineStr"/>
-      <c r="P13" s="4" t="inlineStr"/>
-      <c r="Q13" s="4" t="inlineStr"/>
-      <c r="R13" s="4" t="inlineStr"/>
-      <c r="S13" s="4" t="inlineStr"/>
-      <c r="T13" s="4" t="inlineStr"/>
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>DSAI-IV Second Half</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="n"/>
+      <c r="C13" s="4" t="n"/>
+      <c r="D13" s="4" t="n"/>
+      <c r="E13" s="4" t="n"/>
+      <c r="F13" s="4" t="n"/>
+      <c r="G13" s="4" t="n"/>
+      <c r="H13" s="4" t="n"/>
+      <c r="I13" s="4" t="n"/>
+      <c r="J13" s="4" t="n"/>
+      <c r="K13" s="4" t="n"/>
+      <c r="L13" s="4" t="n"/>
+      <c r="M13" s="4" t="n"/>
+      <c r="N13" s="4" t="n"/>
+      <c r="O13" s="4" t="n"/>
+      <c r="P13" s="4" t="n"/>
+      <c r="Q13" s="4" t="n"/>
+      <c r="R13" s="4" t="n"/>
+      <c r="S13" s="4" t="n"/>
+      <c r="T13" s="4" t="n"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Tuesday</t>
-        </is>
-      </c>
-      <c r="B14" s="4" t="inlineStr"/>
-      <c r="C14" s="11" t="inlineStr">
-        <is>
-          <t>Elective2</t>
-        </is>
-      </c>
-      <c r="D14" s="11" t="n"/>
-      <c r="E14" s="4" t="inlineStr"/>
-      <c r="F14" s="27" t="inlineStr">
-        <is>
-          <t>DA264 (C404)</t>
-        </is>
-      </c>
-      <c r="G14" s="27" t="n"/>
-      <c r="H14" s="27" t="n"/>
-      <c r="I14" s="28" t="inlineStr">
-        <is>
-          <t>DA265T (C405)</t>
-        </is>
-      </c>
-      <c r="J14" s="28" t="n"/>
-      <c r="K14" s="28" t="n"/>
-      <c r="L14" s="4" t="inlineStr"/>
-      <c r="M14" s="4" t="inlineStr"/>
-      <c r="N14" s="4" t="inlineStr"/>
-      <c r="O14" s="4" t="inlineStr"/>
-      <c r="P14" s="4" t="inlineStr"/>
-      <c r="Q14" s="4" t="inlineStr"/>
-      <c r="R14" s="4" t="inlineStr"/>
-      <c r="S14" s="4" t="inlineStr"/>
-      <c r="T14" s="4" t="inlineStr"/>
+          <t>Day</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>07:30-09:00</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t>09:00-10:00</t>
+        </is>
+      </c>
+      <c r="D14" s="3" t="inlineStr">
+        <is>
+          <t>10:00-10:30</t>
+        </is>
+      </c>
+      <c r="E14" s="3" t="inlineStr">
+        <is>
+          <t>10:30-10:45</t>
+        </is>
+      </c>
+      <c r="F14" s="3" t="inlineStr">
+        <is>
+          <t>10:45-11:00</t>
+        </is>
+      </c>
+      <c r="G14" s="3" t="inlineStr">
+        <is>
+          <t>11:00-12:00</t>
+        </is>
+      </c>
+      <c r="H14" s="3" t="inlineStr">
+        <is>
+          <t>12:00-12:15</t>
+        </is>
+      </c>
+      <c r="I14" s="3" t="inlineStr">
+        <is>
+          <t>12:15-12:30</t>
+        </is>
+      </c>
+      <c r="J14" s="3" t="inlineStr">
+        <is>
+          <t>12:30-12:45</t>
+        </is>
+      </c>
+      <c r="K14" s="3" t="inlineStr">
+        <is>
+          <t>12:45-13:15</t>
+        </is>
+      </c>
+      <c r="L14" s="3" t="inlineStr">
+        <is>
+          <t>13:15-14:00</t>
+        </is>
+      </c>
+      <c r="M14" s="3" t="inlineStr">
+        <is>
+          <t>14:00-14:30</t>
+        </is>
+      </c>
+      <c r="N14" s="3" t="inlineStr">
+        <is>
+          <t>14:30-15:30</t>
+        </is>
+      </c>
+      <c r="O14" s="3" t="inlineStr">
+        <is>
+          <t>15:30-15:40</t>
+        </is>
+      </c>
+      <c r="P14" s="3" t="inlineStr">
+        <is>
+          <t>15:40-16:00</t>
+        </is>
+      </c>
+      <c r="Q14" s="3" t="inlineStr">
+        <is>
+          <t>16:00-16:30</t>
+        </is>
+      </c>
+      <c r="R14" s="3" t="inlineStr">
+        <is>
+          <t>16:30-17:10</t>
+        </is>
+      </c>
+      <c r="S14" s="3" t="inlineStr">
+        <is>
+          <t>17:10-17:30</t>
+        </is>
+      </c>
+      <c r="T14" s="3" t="inlineStr">
+        <is>
+          <t>17:30-18:30</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Wednesday</t>
+          <t>Monday</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr"/>
       <c r="C15" s="11" t="inlineStr">
         <is>
-          <t>Elective2T</t>
-        </is>
-      </c>
-      <c r="D15" s="4" t="inlineStr"/>
+          <t>Elective2</t>
+        </is>
+      </c>
+      <c r="D15" s="11" t="n"/>
       <c r="E15" s="4" t="inlineStr"/>
-      <c r="F15" s="27" t="inlineStr">
-        <is>
-          <t>DA264 (C404)</t>
-        </is>
-      </c>
-      <c r="G15" s="27" t="n"/>
-      <c r="H15" s="27" t="n"/>
+      <c r="F15" s="29" t="inlineStr">
+        <is>
+          <t>DA263T (C403)</t>
+        </is>
+      </c>
+      <c r="G15" s="29" t="n"/>
+      <c r="H15" s="4" t="inlineStr"/>
       <c r="I15" s="4" t="inlineStr"/>
       <c r="J15" s="4" t="inlineStr"/>
       <c r="K15" s="4" t="inlineStr"/>
       <c r="L15" s="4" t="inlineStr"/>
-      <c r="M15" s="25" t="inlineStr">
-        <is>
-          <t>HS261 (C403)</t>
-        </is>
-      </c>
-      <c r="N15" s="25" t="n"/>
+      <c r="M15" s="28" t="inlineStr">
+        <is>
+          <t>DA265 (C405)</t>
+        </is>
+      </c>
+      <c r="N15" s="28" t="n"/>
       <c r="O15" s="4" t="inlineStr"/>
       <c r="P15" s="4" t="inlineStr"/>
       <c r="Q15" s="4" t="inlineStr"/>
@@ -10877,34 +10853,34 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Thursday</t>
+          <t>Tuesday</t>
         </is>
       </c>
       <c r="B16" s="4" t="inlineStr"/>
-      <c r="C16" s="29" t="inlineStr">
-        <is>
-          <t>DA263 (C403)</t>
-        </is>
-      </c>
-      <c r="D16" s="29" t="n"/>
+      <c r="C16" s="11" t="inlineStr">
+        <is>
+          <t>Elective2</t>
+        </is>
+      </c>
+      <c r="D16" s="11" t="n"/>
       <c r="E16" s="4" t="inlineStr"/>
       <c r="F16" s="27" t="inlineStr">
         <is>
-          <t>DA264 (Lab-L406)</t>
+          <t>DA264 (C404)</t>
         </is>
       </c>
       <c r="G16" s="27" t="n"/>
       <c r="H16" s="27" t="n"/>
-      <c r="I16" s="27" t="n"/>
-      <c r="J16" s="27" t="n"/>
-      <c r="K16" s="4" t="inlineStr"/>
+      <c r="I16" s="28" t="inlineStr">
+        <is>
+          <t>DA265T (C405)</t>
+        </is>
+      </c>
+      <c r="J16" s="28" t="n"/>
+      <c r="K16" s="28" t="n"/>
       <c r="L16" s="4" t="inlineStr"/>
-      <c r="M16" s="25" t="inlineStr">
-        <is>
-          <t>HS261 (C403)</t>
-        </is>
-      </c>
-      <c r="N16" s="25" t="n"/>
+      <c r="M16" s="4" t="inlineStr"/>
+      <c r="N16" s="4" t="inlineStr"/>
       <c r="O16" s="4" t="inlineStr"/>
       <c r="P16" s="4" t="inlineStr"/>
       <c r="Q16" s="4" t="inlineStr"/>
@@ -10915,30 +10891,34 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Friday</t>
+          <t>Wednesday</t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr"/>
-      <c r="C17" s="28" t="inlineStr">
-        <is>
-          <t>DA265 (C405)</t>
-        </is>
-      </c>
-      <c r="D17" s="28" t="n"/>
+      <c r="C17" s="11" t="inlineStr">
+        <is>
+          <t>Elective2T</t>
+        </is>
+      </c>
+      <c r="D17" s="4" t="inlineStr"/>
       <c r="E17" s="4" t="inlineStr"/>
-      <c r="F17" s="29" t="inlineStr">
-        <is>
-          <t>DA263 (C403)</t>
-        </is>
-      </c>
-      <c r="G17" s="29" t="n"/>
-      <c r="H17" s="29" t="n"/>
+      <c r="F17" s="27" t="inlineStr">
+        <is>
+          <t>DA264 (C404)</t>
+        </is>
+      </c>
+      <c r="G17" s="27" t="n"/>
+      <c r="H17" s="27" t="n"/>
       <c r="I17" s="4" t="inlineStr"/>
       <c r="J17" s="4" t="inlineStr"/>
       <c r="K17" s="4" t="inlineStr"/>
       <c r="L17" s="4" t="inlineStr"/>
-      <c r="M17" s="4" t="inlineStr"/>
-      <c r="N17" s="4" t="inlineStr"/>
+      <c r="M17" s="25" t="inlineStr">
+        <is>
+          <t>HS261 (C403)</t>
+        </is>
+      </c>
+      <c r="N17" s="25" t="n"/>
       <c r="O17" s="4" t="inlineStr"/>
       <c r="P17" s="4" t="inlineStr"/>
       <c r="Q17" s="4" t="inlineStr"/>
@@ -10947,51 +10927,83 @@
       <c r="T17" s="4" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr"/>
-      <c r="B18" s="4" t="n"/>
-      <c r="C18" s="4" t="n"/>
-      <c r="D18" s="4" t="n"/>
-      <c r="E18" s="4" t="n"/>
-      <c r="F18" s="4" t="n"/>
-      <c r="G18" s="4" t="n"/>
-      <c r="H18" s="4" t="n"/>
-      <c r="I18" s="4" t="n"/>
-      <c r="J18" s="4" t="n"/>
-      <c r="K18" s="4" t="n"/>
-      <c r="L18" s="4" t="n"/>
-      <c r="M18" s="4" t="n"/>
-      <c r="N18" s="4" t="n"/>
-      <c r="O18" s="4" t="n"/>
-      <c r="P18" s="4" t="n"/>
-      <c r="Q18" s="4" t="n"/>
-      <c r="R18" s="4" t="n"/>
-      <c r="S18" s="4" t="n"/>
-      <c r="T18" s="4" t="n"/>
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Thursday</t>
+        </is>
+      </c>
+      <c r="B18" s="4" t="inlineStr"/>
+      <c r="C18" s="29" t="inlineStr">
+        <is>
+          <t>DA263 (C403)</t>
+        </is>
+      </c>
+      <c r="D18" s="29" t="n"/>
+      <c r="E18" s="4" t="inlineStr"/>
+      <c r="F18" s="27" t="inlineStr">
+        <is>
+          <t>DA264 (Lab-L406)</t>
+        </is>
+      </c>
+      <c r="G18" s="27" t="n"/>
+      <c r="H18" s="27" t="n"/>
+      <c r="I18" s="27" t="n"/>
+      <c r="J18" s="27" t="n"/>
+      <c r="K18" s="4" t="inlineStr"/>
+      <c r="L18" s="4" t="inlineStr"/>
+      <c r="M18" s="25" t="inlineStr">
+        <is>
+          <t>HS261 (C403)</t>
+        </is>
+      </c>
+      <c r="N18" s="25" t="n"/>
+      <c r="O18" s="4" t="inlineStr"/>
+      <c r="P18" s="4" t="inlineStr"/>
+      <c r="Q18" s="4" t="inlineStr"/>
+      <c r="R18" s="4" t="inlineStr"/>
+      <c r="S18" s="4" t="inlineStr"/>
+      <c r="T18" s="4" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" t="inlineStr"/>
-      <c r="B19" s="4" t="n"/>
-      <c r="C19" s="4" t="n"/>
-      <c r="D19" s="4" t="n"/>
-      <c r="E19" s="4" t="n"/>
-      <c r="F19" s="4" t="n"/>
-      <c r="G19" s="4" t="n"/>
-      <c r="H19" s="4" t="n"/>
-      <c r="I19" s="4" t="n"/>
-      <c r="J19" s="4" t="n"/>
-      <c r="K19" s="4" t="n"/>
-      <c r="L19" s="4" t="n"/>
-      <c r="M19" s="4" t="n"/>
-      <c r="N19" s="4" t="n"/>
-      <c r="O19" s="4" t="n"/>
-      <c r="P19" s="4" t="n"/>
-      <c r="Q19" s="4" t="n"/>
-      <c r="R19" s="4" t="n"/>
-      <c r="S19" s="4" t="n"/>
-      <c r="T19" s="4" t="n"/>
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Friday</t>
+        </is>
+      </c>
+      <c r="B19" s="4" t="inlineStr"/>
+      <c r="C19" s="28" t="inlineStr">
+        <is>
+          <t>DA265 (C405)</t>
+        </is>
+      </c>
+      <c r="D19" s="28" t="n"/>
+      <c r="E19" s="4" t="inlineStr"/>
+      <c r="F19" s="29" t="inlineStr">
+        <is>
+          <t>DA263 (C403)</t>
+        </is>
+      </c>
+      <c r="G19" s="29" t="n"/>
+      <c r="H19" s="29" t="n"/>
+      <c r="I19" s="4" t="inlineStr"/>
+      <c r="J19" s="4" t="inlineStr"/>
+      <c r="K19" s="4" t="inlineStr"/>
+      <c r="L19" s="4" t="inlineStr"/>
+      <c r="M19" s="4" t="inlineStr"/>
+      <c r="N19" s="4" t="inlineStr"/>
+      <c r="O19" s="4" t="inlineStr"/>
+      <c r="P19" s="4" t="inlineStr"/>
+      <c r="Q19" s="4" t="inlineStr"/>
+      <c r="R19" s="4" t="inlineStr"/>
+      <c r="S19" s="4" t="inlineStr"/>
+      <c r="T19" s="4" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" t="inlineStr"/>
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>WARNING: Courses missing from generated timetable output</t>
+        </is>
+      </c>
       <c r="B20" s="4" t="n"/>
       <c r="C20" s="4" t="n"/>
       <c r="D20" s="4" t="n"/>
@@ -11013,9 +11025,9 @@
       <c r="T20" s="4" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" s="13" t="inlineStr">
-        <is>
-          <t>Legend - DSAI IV</t>
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>DS308: combined-course constraints prevented placement</t>
         </is>
       </c>
       <c r="B21" s="4" t="n"/>
@@ -11039,46 +11051,14 @@
       <c r="T21" s="4" t="n"/>
     </row>
     <row r="22">
-      <c r="A22" s="14" t="inlineStr">
-        <is>
-          <t>Course Code</t>
-        </is>
-      </c>
-      <c r="B22" s="15" t="inlineStr">
-        <is>
-          <t>Course Title</t>
-        </is>
-      </c>
-      <c r="C22" s="15" t="inlineStr">
-        <is>
-          <t>L-T-P-S-C</t>
-        </is>
-      </c>
-      <c r="D22" s="15" t="inlineStr">
-        <is>
-          <t>Faculty</t>
-        </is>
-      </c>
-      <c r="E22" s="15" t="inlineStr">
-        <is>
-          <t>Semester Half</t>
-        </is>
-      </c>
-      <c r="F22" s="16" t="inlineStr">
-        <is>
-          <t>Elective</t>
-        </is>
-      </c>
-      <c r="G22" s="16" t="inlineStr">
-        <is>
-          <t>Elective Basket</t>
-        </is>
-      </c>
-      <c r="H22" s="16" t="inlineStr">
-        <is>
-          <t>Elective Room</t>
-        </is>
-      </c>
+      <c r="A22" t="inlineStr"/>
+      <c r="B22" s="4" t="n"/>
+      <c r="C22" s="4" t="n"/>
+      <c r="D22" s="4" t="n"/>
+      <c r="E22" s="4" t="n"/>
+      <c r="F22" s="4" t="n"/>
+      <c r="G22" s="4" t="n"/>
+      <c r="H22" s="4" t="n"/>
       <c r="I22" s="4" t="n"/>
       <c r="J22" s="4" t="n"/>
       <c r="K22" s="4" t="n"/>
@@ -11093,42 +11073,14 @@
       <c r="T22" s="4" t="n"/>
     </row>
     <row r="23">
-      <c r="A23" s="17" t="inlineStr">
-        <is>
-          <t>DA263</t>
-        </is>
-      </c>
-      <c r="B23" s="3" t="inlineStr">
-        <is>
-          <t>Big Data Analytics</t>
-        </is>
-      </c>
-      <c r="C23" s="3" t="inlineStr">
-        <is>
-          <t>3-1-0-0-4</t>
-        </is>
-      </c>
-      <c r="D23" s="3" t="inlineStr">
-        <is>
-          <t>Dr. Animesh Chaturvedi</t>
-        </is>
-      </c>
-      <c r="E23" s="3" t="inlineStr">
-        <is>
-          <t>Full Sem</t>
-        </is>
-      </c>
-      <c r="F23" s="3" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G23" s="3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H23" s="4" t="inlineStr"/>
+      <c r="A23" t="inlineStr"/>
+      <c r="B23" s="4" t="n"/>
+      <c r="C23" s="4" t="n"/>
+      <c r="D23" s="4" t="n"/>
+      <c r="E23" s="4" t="n"/>
+      <c r="F23" s="4" t="n"/>
+      <c r="G23" s="4" t="n"/>
+      <c r="H23" s="4" t="n"/>
       <c r="I23" s="4" t="n"/>
       <c r="J23" s="4" t="n"/>
       <c r="K23" s="4" t="n"/>
@@ -11143,42 +11095,14 @@
       <c r="T23" s="4" t="n"/>
     </row>
     <row r="24">
-      <c r="A24" s="17" t="inlineStr">
-        <is>
-          <t>DA264</t>
-        </is>
-      </c>
-      <c r="B24" s="3" t="inlineStr">
-        <is>
-          <t>Database Management and Warehousing</t>
-        </is>
-      </c>
-      <c r="C24" s="3" t="inlineStr">
-        <is>
-          <t>3-0-2-0-4</t>
-        </is>
-      </c>
-      <c r="D24" s="3" t="inlineStr">
-        <is>
-          <t>Dr. Utkarsh Mahadeo Khaire</t>
-        </is>
-      </c>
-      <c r="E24" s="3" t="inlineStr">
-        <is>
-          <t>Full Sem</t>
-        </is>
-      </c>
-      <c r="F24" s="3" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G24" s="3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H24" s="4" t="inlineStr"/>
+      <c r="A24" t="inlineStr"/>
+      <c r="B24" s="4" t="n"/>
+      <c r="C24" s="4" t="n"/>
+      <c r="D24" s="4" t="n"/>
+      <c r="E24" s="4" t="n"/>
+      <c r="F24" s="4" t="n"/>
+      <c r="G24" s="4" t="n"/>
+      <c r="H24" s="4" t="n"/>
       <c r="I24" s="4" t="n"/>
       <c r="J24" s="4" t="n"/>
       <c r="K24" s="4" t="n"/>
@@ -11193,42 +11117,18 @@
       <c r="T24" s="4" t="n"/>
     </row>
     <row r="25">
-      <c r="A25" s="17" t="inlineStr">
-        <is>
-          <t>DA265</t>
-        </is>
-      </c>
-      <c r="B25" s="3" t="inlineStr">
-        <is>
-          <t>Deep Learning</t>
-        </is>
-      </c>
-      <c r="C25" s="3" t="inlineStr">
-        <is>
-          <t>3-1-0-0-4</t>
-        </is>
-      </c>
-      <c r="D25" s="3" t="inlineStr">
-        <is>
-          <t>Dr. Shirshendu Layek</t>
-        </is>
-      </c>
-      <c r="E25" s="3" t="inlineStr">
-        <is>
-          <t>Full Sem</t>
-        </is>
-      </c>
-      <c r="F25" s="3" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G25" s="3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H25" s="4" t="inlineStr"/>
+      <c r="A25" s="13" t="inlineStr">
+        <is>
+          <t>Legend - DSAI IV</t>
+        </is>
+      </c>
+      <c r="B25" s="4" t="n"/>
+      <c r="C25" s="4" t="n"/>
+      <c r="D25" s="4" t="n"/>
+      <c r="E25" s="4" t="n"/>
+      <c r="F25" s="4" t="n"/>
+      <c r="G25" s="4" t="n"/>
+      <c r="H25" s="4" t="n"/>
       <c r="I25" s="4" t="n"/>
       <c r="J25" s="4" t="n"/>
       <c r="K25" s="4" t="n"/>
@@ -11243,42 +11143,46 @@
       <c r="T25" s="4" t="n"/>
     </row>
     <row r="26">
-      <c r="A26" s="17" t="inlineStr">
-        <is>
-          <t>DS308</t>
-        </is>
-      </c>
-      <c r="B26" s="3" t="inlineStr">
-        <is>
-          <t>Data Security and Privacy</t>
-        </is>
-      </c>
-      <c r="C26" s="3" t="inlineStr">
-        <is>
-          <t>3-1-0-4-4</t>
-        </is>
-      </c>
-      <c r="D26" s="3" t="inlineStr">
-        <is>
-          <t>Dr. Girish Revadigar</t>
-        </is>
-      </c>
-      <c r="E26" s="3" t="inlineStr">
-        <is>
-          <t>Full Sem</t>
-        </is>
-      </c>
-      <c r="F26" s="3" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G26" s="3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H26" s="4" t="inlineStr"/>
+      <c r="A26" s="14" t="inlineStr">
+        <is>
+          <t>Course Code</t>
+        </is>
+      </c>
+      <c r="B26" s="15" t="inlineStr">
+        <is>
+          <t>Course Title</t>
+        </is>
+      </c>
+      <c r="C26" s="15" t="inlineStr">
+        <is>
+          <t>L-T-P-S-C</t>
+        </is>
+      </c>
+      <c r="D26" s="15" t="inlineStr">
+        <is>
+          <t>Faculty</t>
+        </is>
+      </c>
+      <c r="E26" s="15" t="inlineStr">
+        <is>
+          <t>Semester Half</t>
+        </is>
+      </c>
+      <c r="F26" s="16" t="inlineStr">
+        <is>
+          <t>Elective</t>
+        </is>
+      </c>
+      <c r="G26" s="16" t="inlineStr">
+        <is>
+          <t>Elective Basket</t>
+        </is>
+      </c>
+      <c r="H26" s="16" t="inlineStr">
+        <is>
+          <t>Elective Room</t>
+        </is>
+      </c>
       <c r="I26" s="4" t="n"/>
       <c r="J26" s="4" t="n"/>
       <c r="K26" s="4" t="n"/>
@@ -11295,22 +11199,22 @@
     <row r="27">
       <c r="A27" s="17" t="inlineStr">
         <is>
-          <t>HS261</t>
+          <t>DA263</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>Ethics and Values / Environmental Studies</t>
+          <t>Big Data Analytics</t>
         </is>
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t>3-0-0-0-3</t>
+          <t>3-1-0-0-4</t>
         </is>
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t>Dr. Aswath Babu H</t>
+          <t>Dr. Animesh Chaturvedi</t>
         </is>
       </c>
       <c r="E27" s="3" t="inlineStr">
@@ -11345,44 +11249,40 @@
     <row r="28">
       <c r="A28" s="17" t="inlineStr">
         <is>
-          <t>EC255</t>
+          <t>DA264</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>Embedded Intelligent Sensing Systems</t>
+          <t>Database Management and Warehousing</t>
         </is>
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t>2-0-2-4-2</t>
+          <t>3-0-2-0-4</t>
         </is>
       </c>
       <c r="D28" s="3" t="inlineStr">
         <is>
-          <t>Dr. Sibasankar Padhy</t>
+          <t>Dr. Utkarsh Mahadeo Khaire</t>
         </is>
       </c>
       <c r="E28" s="3" t="inlineStr">
         <is>
-          <t>First Half</t>
+          <t>Full Sem</t>
         </is>
       </c>
       <c r="F28" s="3" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="G28" s="3" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H28" s="3" t="inlineStr">
-        <is>
-          <t>C301</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H28" s="4" t="inlineStr"/>
       <c r="I28" s="4" t="n"/>
       <c r="J28" s="4" t="n"/>
       <c r="K28" s="4" t="n"/>
@@ -11399,44 +11299,40 @@
     <row r="29">
       <c r="A29" s="17" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>DA265</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>Edge AI Systems Design</t>
+          <t>Deep Learning</t>
         </is>
       </c>
       <c r="C29" s="3" t="inlineStr">
         <is>
-          <t>3-1-0-0-2</t>
+          <t>3-1-0-0-4</t>
         </is>
       </c>
       <c r="D29" s="3" t="inlineStr">
         <is>
-          <t>Dr. Deepak K T</t>
+          <t>Dr. Shirshendu Layek</t>
         </is>
       </c>
       <c r="E29" s="3" t="inlineStr">
         <is>
-          <t>First Half</t>
+          <t>Full Sem</t>
         </is>
       </c>
       <c r="F29" s="3" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="G29" s="3" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H29" s="3" t="inlineStr">
-        <is>
-          <t>C102</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H29" s="4" t="inlineStr"/>
       <c r="I29" s="4" t="n"/>
       <c r="J29" s="4" t="n"/>
       <c r="K29" s="4" t="n"/>
@@ -11453,44 +11349,40 @@
     <row r="30">
       <c r="A30" s="17" t="inlineStr">
         <is>
-          <t>CS252</t>
+          <t>DS308</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>Digital Forensic</t>
+          <t>Data Security and Privacy</t>
         </is>
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
-          <t>3-1-0-0-2</t>
+          <t>3-1-0-4-4</t>
         </is>
       </c>
       <c r="D30" s="3" t="inlineStr">
         <is>
-          <t>Dr. Abdul Wahid</t>
+          <t>Dr. Girish Revadigar</t>
         </is>
       </c>
       <c r="E30" s="3" t="inlineStr">
         <is>
-          <t>Second Half</t>
+          <t>Full Sem</t>
         </is>
       </c>
       <c r="F30" s="3" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="G30" s="3" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="H30" s="3" t="inlineStr">
-        <is>
-          <t>C401</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H30" s="4" t="inlineStr"/>
       <c r="I30" s="4" t="n"/>
       <c r="J30" s="4" t="n"/>
       <c r="K30" s="4" t="n"/>
@@ -11507,44 +11399,40 @@
     <row r="31">
       <c r="A31" s="17" t="inlineStr">
         <is>
-          <t>CS261</t>
+          <t>HS261</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>Operating System</t>
+          <t>Ethics and Values / Environmental Studies</t>
         </is>
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t>3-1-0-0-2</t>
+          <t>3-0-0-0-3</t>
         </is>
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t>Dr. Siddharth R</t>
+          <t>Dr. Aswath Babu H</t>
         </is>
       </c>
       <c r="E31" s="3" t="inlineStr">
         <is>
-          <t>Second Half</t>
+          <t>Full Sem</t>
         </is>
       </c>
       <c r="F31" s="3" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="G31" s="3" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="H31" s="3" t="inlineStr">
-        <is>
-          <t>C003</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H31" s="4" t="inlineStr"/>
       <c r="I31" s="4" t="n"/>
       <c r="J31" s="4" t="n"/>
       <c r="K31" s="4" t="n"/>
@@ -11561,27 +11449,27 @@
     <row r="32">
       <c r="A32" s="17" t="inlineStr">
         <is>
-          <t>EC257</t>
+          <t>EC255</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>Causal Inference</t>
+          <t>Embedded Intelligent Sensing Systems</t>
         </is>
       </c>
       <c r="C32" s="3" t="inlineStr">
         <is>
-          <t>3-1-0-0-2</t>
+          <t>2-0-2-4-2</t>
         </is>
       </c>
       <c r="D32" s="3" t="inlineStr">
         <is>
-          <t>Dr. Chinmayananda A</t>
+          <t>Dr. Sibasankar Padhy</t>
         </is>
       </c>
       <c r="E32" s="3" t="inlineStr">
         <is>
-          <t>Second Half</t>
+          <t>First Half</t>
         </is>
       </c>
       <c r="F32" s="3" t="inlineStr">
@@ -11591,12 +11479,12 @@
       </c>
       <c r="G32" s="3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H32" s="3" t="inlineStr">
         <is>
-          <t>C302</t>
+          <t>C301</t>
         </is>
       </c>
       <c r="I32" s="4" t="n"/>
@@ -11615,12 +11503,12 @@
     <row r="33">
       <c r="A33" s="17" t="inlineStr">
         <is>
-          <t>CS253</t>
+          <t>NEW</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>Time Series Forecasting and Applications</t>
+          <t>Edge AI Systems Design</t>
         </is>
       </c>
       <c r="C33" s="3" t="inlineStr">
@@ -11630,12 +11518,12 @@
       </c>
       <c r="D33" s="3" t="inlineStr">
         <is>
-          <t>Dr. Nataraj</t>
+          <t>Dr. Deepak K T</t>
         </is>
       </c>
       <c r="E33" s="3" t="inlineStr">
         <is>
-          <t>Second Half</t>
+          <t>First Half</t>
         </is>
       </c>
       <c r="F33" s="3" t="inlineStr">
@@ -11645,12 +11533,12 @@
       </c>
       <c r="G33" s="3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H33" s="3" t="inlineStr">
         <is>
-          <t>C303</t>
+          <t>C102</t>
         </is>
       </c>
       <c r="I33" s="4" t="n"/>
@@ -11667,14 +11555,46 @@
       <c r="T33" s="4" t="n"/>
     </row>
     <row r="34">
-      <c r="A34" t="inlineStr"/>
-      <c r="B34" s="4" t="n"/>
-      <c r="C34" s="4" t="n"/>
-      <c r="D34" s="4" t="n"/>
-      <c r="E34" s="4" t="n"/>
-      <c r="F34" s="4" t="n"/>
-      <c r="G34" s="4" t="n"/>
-      <c r="H34" s="4" t="n"/>
+      <c r="A34" s="17" t="inlineStr">
+        <is>
+          <t>CS252</t>
+        </is>
+      </c>
+      <c r="B34" s="3" t="inlineStr">
+        <is>
+          <t>Digital Forensic</t>
+        </is>
+      </c>
+      <c r="C34" s="3" t="inlineStr">
+        <is>
+          <t>3-1-0-0-2</t>
+        </is>
+      </c>
+      <c r="D34" s="3" t="inlineStr">
+        <is>
+          <t>Dr. Abdul Wahid</t>
+        </is>
+      </c>
+      <c r="E34" s="3" t="inlineStr">
+        <is>
+          <t>Second Half</t>
+        </is>
+      </c>
+      <c r="F34" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G34" s="3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H34" s="3" t="inlineStr">
+        <is>
+          <t>C401</t>
+        </is>
+      </c>
       <c r="I34" s="4" t="n"/>
       <c r="J34" s="4" t="n"/>
       <c r="K34" s="4" t="n"/>
@@ -11688,32 +11608,216 @@
       <c r="S34" s="4" t="n"/>
       <c r="T34" s="4" t="n"/>
     </row>
+    <row r="35">
+      <c r="A35" s="17" t="inlineStr">
+        <is>
+          <t>CS261</t>
+        </is>
+      </c>
+      <c r="B35" s="3" t="inlineStr">
+        <is>
+          <t>Operating System</t>
+        </is>
+      </c>
+      <c r="C35" s="3" t="inlineStr">
+        <is>
+          <t>3-1-0-0-2</t>
+        </is>
+      </c>
+      <c r="D35" s="3" t="inlineStr">
+        <is>
+          <t>Dr. Siddharth R</t>
+        </is>
+      </c>
+      <c r="E35" s="3" t="inlineStr">
+        <is>
+          <t>Second Half</t>
+        </is>
+      </c>
+      <c r="F35" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G35" s="3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H35" s="3" t="inlineStr">
+        <is>
+          <t>C003</t>
+        </is>
+      </c>
+      <c r="I35" s="4" t="n"/>
+      <c r="J35" s="4" t="n"/>
+      <c r="K35" s="4" t="n"/>
+      <c r="L35" s="4" t="n"/>
+      <c r="M35" s="4" t="n"/>
+      <c r="N35" s="4" t="n"/>
+      <c r="O35" s="4" t="n"/>
+      <c r="P35" s="4" t="n"/>
+      <c r="Q35" s="4" t="n"/>
+      <c r="R35" s="4" t="n"/>
+      <c r="S35" s="4" t="n"/>
+      <c r="T35" s="4" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="17" t="inlineStr">
+        <is>
+          <t>EC257</t>
+        </is>
+      </c>
+      <c r="B36" s="3" t="inlineStr">
+        <is>
+          <t>Causal Inference</t>
+        </is>
+      </c>
+      <c r="C36" s="3" t="inlineStr">
+        <is>
+          <t>3-1-0-0-2</t>
+        </is>
+      </c>
+      <c r="D36" s="3" t="inlineStr">
+        <is>
+          <t>Dr. Chinmayananda A</t>
+        </is>
+      </c>
+      <c r="E36" s="3" t="inlineStr">
+        <is>
+          <t>Second Half</t>
+        </is>
+      </c>
+      <c r="F36" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G36" s="3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H36" s="3" t="inlineStr">
+        <is>
+          <t>C302</t>
+        </is>
+      </c>
+      <c r="I36" s="4" t="n"/>
+      <c r="J36" s="4" t="n"/>
+      <c r="K36" s="4" t="n"/>
+      <c r="L36" s="4" t="n"/>
+      <c r="M36" s="4" t="n"/>
+      <c r="N36" s="4" t="n"/>
+      <c r="O36" s="4" t="n"/>
+      <c r="P36" s="4" t="n"/>
+      <c r="Q36" s="4" t="n"/>
+      <c r="R36" s="4" t="n"/>
+      <c r="S36" s="4" t="n"/>
+      <c r="T36" s="4" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="17" t="inlineStr">
+        <is>
+          <t>CS253</t>
+        </is>
+      </c>
+      <c r="B37" s="3" t="inlineStr">
+        <is>
+          <t>Time Series Forecasting and Applications</t>
+        </is>
+      </c>
+      <c r="C37" s="3" t="inlineStr">
+        <is>
+          <t>3-1-0-0-2</t>
+        </is>
+      </c>
+      <c r="D37" s="3" t="inlineStr">
+        <is>
+          <t>Dr. Nataraj</t>
+        </is>
+      </c>
+      <c r="E37" s="3" t="inlineStr">
+        <is>
+          <t>Second Half</t>
+        </is>
+      </c>
+      <c r="F37" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G37" s="3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H37" s="3" t="inlineStr">
+        <is>
+          <t>C303</t>
+        </is>
+      </c>
+      <c r="I37" s="4" t="n"/>
+      <c r="J37" s="4" t="n"/>
+      <c r="K37" s="4" t="n"/>
+      <c r="L37" s="4" t="n"/>
+      <c r="M37" s="4" t="n"/>
+      <c r="N37" s="4" t="n"/>
+      <c r="O37" s="4" t="n"/>
+      <c r="P37" s="4" t="n"/>
+      <c r="Q37" s="4" t="n"/>
+      <c r="R37" s="4" t="n"/>
+      <c r="S37" s="4" t="n"/>
+      <c r="T37" s="4" t="n"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr"/>
+      <c r="B38" s="4" t="n"/>
+      <c r="C38" s="4" t="n"/>
+      <c r="D38" s="4" t="n"/>
+      <c r="E38" s="4" t="n"/>
+      <c r="F38" s="4" t="n"/>
+      <c r="G38" s="4" t="n"/>
+      <c r="H38" s="4" t="n"/>
+      <c r="I38" s="4" t="n"/>
+      <c r="J38" s="4" t="n"/>
+      <c r="K38" s="4" t="n"/>
+      <c r="L38" s="4" t="n"/>
+      <c r="M38" s="4" t="n"/>
+      <c r="N38" s="4" t="n"/>
+      <c r="O38" s="4" t="n"/>
+      <c r="P38" s="4" t="n"/>
+      <c r="Q38" s="4" t="n"/>
+      <c r="R38" s="4" t="n"/>
+      <c r="S38" s="4" t="n"/>
+      <c r="T38" s="4" t="n"/>
+    </row>
   </sheetData>
   <mergeCells count="26">
+    <mergeCell ref="I16:K16"/>
     <mergeCell ref="C6:D6"/>
     <mergeCell ref="F5:H5"/>
+    <mergeCell ref="C15:D15"/>
     <mergeCell ref="O4:Q4"/>
-    <mergeCell ref="F16:J16"/>
     <mergeCell ref="C5:D5"/>
     <mergeCell ref="F8:H8"/>
-    <mergeCell ref="C14:D14"/>
     <mergeCell ref="M5:N5"/>
     <mergeCell ref="F17:H17"/>
     <mergeCell ref="F6:J6"/>
+    <mergeCell ref="C18:D18"/>
     <mergeCell ref="C4:D4"/>
     <mergeCell ref="C16:D16"/>
-    <mergeCell ref="I14:K14"/>
-    <mergeCell ref="M13:N13"/>
-    <mergeCell ref="M16:N16"/>
+    <mergeCell ref="F15:G15"/>
+    <mergeCell ref="F18:J18"/>
     <mergeCell ref="M15:N15"/>
-    <mergeCell ref="F14:H14"/>
     <mergeCell ref="M6:N6"/>
-    <mergeCell ref="F13:G13"/>
-    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="M18:N18"/>
+    <mergeCell ref="M17:N17"/>
+    <mergeCell ref="F16:H16"/>
     <mergeCell ref="C7:D7"/>
-    <mergeCell ref="C13:D13"/>
+    <mergeCell ref="F19:H19"/>
+    <mergeCell ref="C19:D19"/>
     <mergeCell ref="F7:H7"/>
-    <mergeCell ref="F15:H15"/>
     <mergeCell ref="M4:N4"/>
     <mergeCell ref="F4:J4"/>
   </mergeCells>

--- a/Balanced_Timetable_latest.xlsx
+++ b/Balanced_Timetable_latest.xlsx
@@ -10246,10 +10246,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T38"/>
+  <dimension ref="A1:T34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="58" customWidth="1" min="1" max="1"/>
+    <col width="21" customWidth="1" min="1" max="1"/>
     <col width="43" customWidth="1" min="2" max="2"/>
     <col width="15" customWidth="1" min="3" max="3"/>
     <col width="28" customWidth="1" min="4" max="4"/>
@@ -10589,11 +10589,7 @@
       <c r="T8" s="4" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>WARNING: Courses missing from generated timetable output</t>
-        </is>
-      </c>
+      <c r="A9" t="inlineStr"/>
       <c r="B9" s="4" t="n"/>
       <c r="C9" s="4" t="n"/>
       <c r="D9" s="4" t="n"/>
@@ -10615,11 +10611,7 @@
       <c r="T9" s="4" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>DS308: combined-course constraints prevented placement</t>
-        </is>
-      </c>
+      <c r="A10" t="inlineStr"/>
       <c r="B10" s="4" t="n"/>
       <c r="C10" s="4" t="n"/>
       <c r="D10" s="4" t="n"/>
@@ -10641,7 +10633,11 @@
       <c r="T10" s="4" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr"/>
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>DSAI-IV Second Half</t>
+        </is>
+      </c>
       <c r="B11" s="4" t="n"/>
       <c r="C11" s="4" t="n"/>
       <c r="D11" s="4" t="n"/>
@@ -10663,186 +10659,214 @@
       <c r="T11" s="4" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr"/>
-      <c r="B12" s="4" t="n"/>
-      <c r="C12" s="4" t="n"/>
-      <c r="D12" s="4" t="n"/>
-      <c r="E12" s="4" t="n"/>
-      <c r="F12" s="4" t="n"/>
-      <c r="G12" s="4" t="n"/>
-      <c r="H12" s="4" t="n"/>
-      <c r="I12" s="4" t="n"/>
-      <c r="J12" s="4" t="n"/>
-      <c r="K12" s="4" t="n"/>
-      <c r="L12" s="4" t="n"/>
-      <c r="M12" s="4" t="n"/>
-      <c r="N12" s="4" t="n"/>
-      <c r="O12" s="4" t="n"/>
-      <c r="P12" s="4" t="n"/>
-      <c r="Q12" s="4" t="n"/>
-      <c r="R12" s="4" t="n"/>
-      <c r="S12" s="4" t="n"/>
-      <c r="T12" s="4" t="n"/>
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Day</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>07:30-09:00</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>09:00-10:00</t>
+        </is>
+      </c>
+      <c r="D12" s="3" t="inlineStr">
+        <is>
+          <t>10:00-10:30</t>
+        </is>
+      </c>
+      <c r="E12" s="3" t="inlineStr">
+        <is>
+          <t>10:30-10:45</t>
+        </is>
+      </c>
+      <c r="F12" s="3" t="inlineStr">
+        <is>
+          <t>10:45-11:00</t>
+        </is>
+      </c>
+      <c r="G12" s="3" t="inlineStr">
+        <is>
+          <t>11:00-12:00</t>
+        </is>
+      </c>
+      <c r="H12" s="3" t="inlineStr">
+        <is>
+          <t>12:00-12:15</t>
+        </is>
+      </c>
+      <c r="I12" s="3" t="inlineStr">
+        <is>
+          <t>12:15-12:30</t>
+        </is>
+      </c>
+      <c r="J12" s="3" t="inlineStr">
+        <is>
+          <t>12:30-12:45</t>
+        </is>
+      </c>
+      <c r="K12" s="3" t="inlineStr">
+        <is>
+          <t>12:45-13:15</t>
+        </is>
+      </c>
+      <c r="L12" s="3" t="inlineStr">
+        <is>
+          <t>13:15-14:00</t>
+        </is>
+      </c>
+      <c r="M12" s="3" t="inlineStr">
+        <is>
+          <t>14:00-14:30</t>
+        </is>
+      </c>
+      <c r="N12" s="3" t="inlineStr">
+        <is>
+          <t>14:30-15:30</t>
+        </is>
+      </c>
+      <c r="O12" s="3" t="inlineStr">
+        <is>
+          <t>15:30-15:40</t>
+        </is>
+      </c>
+      <c r="P12" s="3" t="inlineStr">
+        <is>
+          <t>15:40-16:00</t>
+        </is>
+      </c>
+      <c r="Q12" s="3" t="inlineStr">
+        <is>
+          <t>16:00-16:30</t>
+        </is>
+      </c>
+      <c r="R12" s="3" t="inlineStr">
+        <is>
+          <t>16:30-17:10</t>
+        </is>
+      </c>
+      <c r="S12" s="3" t="inlineStr">
+        <is>
+          <t>17:10-17:30</t>
+        </is>
+      </c>
+      <c r="T12" s="3" t="inlineStr">
+        <is>
+          <t>17:30-18:30</t>
+        </is>
+      </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="inlineStr">
-        <is>
-          <t>DSAI-IV Second Half</t>
-        </is>
-      </c>
-      <c r="B13" s="4" t="n"/>
-      <c r="C13" s="4" t="n"/>
-      <c r="D13" s="4" t="n"/>
-      <c r="E13" s="4" t="n"/>
-      <c r="F13" s="4" t="n"/>
-      <c r="G13" s="4" t="n"/>
-      <c r="H13" s="4" t="n"/>
-      <c r="I13" s="4" t="n"/>
-      <c r="J13" s="4" t="n"/>
-      <c r="K13" s="4" t="n"/>
-      <c r="L13" s="4" t="n"/>
-      <c r="M13" s="4" t="n"/>
-      <c r="N13" s="4" t="n"/>
-      <c r="O13" s="4" t="n"/>
-      <c r="P13" s="4" t="n"/>
-      <c r="Q13" s="4" t="n"/>
-      <c r="R13" s="4" t="n"/>
-      <c r="S13" s="4" t="n"/>
-      <c r="T13" s="4" t="n"/>
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Monday</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="inlineStr"/>
+      <c r="C13" s="11" t="inlineStr">
+        <is>
+          <t>Elective2</t>
+        </is>
+      </c>
+      <c r="D13" s="11" t="n"/>
+      <c r="E13" s="4" t="inlineStr"/>
+      <c r="F13" s="29" t="inlineStr">
+        <is>
+          <t>DA263T (C403)</t>
+        </is>
+      </c>
+      <c r="G13" s="29" t="n"/>
+      <c r="H13" s="4" t="inlineStr"/>
+      <c r="I13" s="4" t="inlineStr"/>
+      <c r="J13" s="4" t="inlineStr"/>
+      <c r="K13" s="4" t="inlineStr"/>
+      <c r="L13" s="4" t="inlineStr"/>
+      <c r="M13" s="28" t="inlineStr">
+        <is>
+          <t>DA265 (C405)</t>
+        </is>
+      </c>
+      <c r="N13" s="28" t="n"/>
+      <c r="O13" s="4" t="inlineStr"/>
+      <c r="P13" s="4" t="inlineStr"/>
+      <c r="Q13" s="4" t="inlineStr"/>
+      <c r="R13" s="4" t="inlineStr"/>
+      <c r="S13" s="4" t="inlineStr"/>
+      <c r="T13" s="4" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Day</t>
-        </is>
-      </c>
-      <c r="B14" s="3" t="inlineStr">
-        <is>
-          <t>07:30-09:00</t>
-        </is>
-      </c>
-      <c r="C14" s="3" t="inlineStr">
-        <is>
-          <t>09:00-10:00</t>
-        </is>
-      </c>
-      <c r="D14" s="3" t="inlineStr">
-        <is>
-          <t>10:00-10:30</t>
-        </is>
-      </c>
-      <c r="E14" s="3" t="inlineStr">
-        <is>
-          <t>10:30-10:45</t>
-        </is>
-      </c>
-      <c r="F14" s="3" t="inlineStr">
-        <is>
-          <t>10:45-11:00</t>
-        </is>
-      </c>
-      <c r="G14" s="3" t="inlineStr">
-        <is>
-          <t>11:00-12:00</t>
-        </is>
-      </c>
-      <c r="H14" s="3" t="inlineStr">
-        <is>
-          <t>12:00-12:15</t>
-        </is>
-      </c>
-      <c r="I14" s="3" t="inlineStr">
-        <is>
-          <t>12:15-12:30</t>
-        </is>
-      </c>
-      <c r="J14" s="3" t="inlineStr">
-        <is>
-          <t>12:30-12:45</t>
-        </is>
-      </c>
-      <c r="K14" s="3" t="inlineStr">
-        <is>
-          <t>12:45-13:15</t>
-        </is>
-      </c>
-      <c r="L14" s="3" t="inlineStr">
-        <is>
-          <t>13:15-14:00</t>
-        </is>
-      </c>
-      <c r="M14" s="3" t="inlineStr">
-        <is>
-          <t>14:00-14:30</t>
-        </is>
-      </c>
-      <c r="N14" s="3" t="inlineStr">
-        <is>
-          <t>14:30-15:30</t>
-        </is>
-      </c>
-      <c r="O14" s="3" t="inlineStr">
-        <is>
-          <t>15:30-15:40</t>
-        </is>
-      </c>
-      <c r="P14" s="3" t="inlineStr">
-        <is>
-          <t>15:40-16:00</t>
-        </is>
-      </c>
-      <c r="Q14" s="3" t="inlineStr">
-        <is>
-          <t>16:00-16:30</t>
-        </is>
-      </c>
-      <c r="R14" s="3" t="inlineStr">
-        <is>
-          <t>16:30-17:10</t>
-        </is>
-      </c>
-      <c r="S14" s="3" t="inlineStr">
-        <is>
-          <t>17:10-17:30</t>
-        </is>
-      </c>
-      <c r="T14" s="3" t="inlineStr">
-        <is>
-          <t>17:30-18:30</t>
-        </is>
-      </c>
+          <t>Tuesday</t>
+        </is>
+      </c>
+      <c r="B14" s="4" t="inlineStr"/>
+      <c r="C14" s="11" t="inlineStr">
+        <is>
+          <t>Elective2</t>
+        </is>
+      </c>
+      <c r="D14" s="11" t="n"/>
+      <c r="E14" s="4" t="inlineStr"/>
+      <c r="F14" s="27" t="inlineStr">
+        <is>
+          <t>DA264 (C404)</t>
+        </is>
+      </c>
+      <c r="G14" s="27" t="n"/>
+      <c r="H14" s="27" t="n"/>
+      <c r="I14" s="28" t="inlineStr">
+        <is>
+          <t>DA265T (C405)</t>
+        </is>
+      </c>
+      <c r="J14" s="28" t="n"/>
+      <c r="K14" s="28" t="n"/>
+      <c r="L14" s="4" t="inlineStr"/>
+      <c r="M14" s="4" t="inlineStr"/>
+      <c r="N14" s="4" t="inlineStr"/>
+      <c r="O14" s="4" t="inlineStr"/>
+      <c r="P14" s="4" t="inlineStr"/>
+      <c r="Q14" s="4" t="inlineStr"/>
+      <c r="R14" s="4" t="inlineStr"/>
+      <c r="S14" s="4" t="inlineStr"/>
+      <c r="T14" s="4" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Monday</t>
+          <t>Wednesday</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr"/>
       <c r="C15" s="11" t="inlineStr">
         <is>
-          <t>Elective2</t>
-        </is>
-      </c>
-      <c r="D15" s="11" t="n"/>
+          <t>Elective2T</t>
+        </is>
+      </c>
+      <c r="D15" s="4" t="inlineStr"/>
       <c r="E15" s="4" t="inlineStr"/>
-      <c r="F15" s="29" t="inlineStr">
-        <is>
-          <t>DA263T (C403)</t>
-        </is>
-      </c>
-      <c r="G15" s="29" t="n"/>
-      <c r="H15" s="4" t="inlineStr"/>
+      <c r="F15" s="27" t="inlineStr">
+        <is>
+          <t>DA264 (C404)</t>
+        </is>
+      </c>
+      <c r="G15" s="27" t="n"/>
+      <c r="H15" s="27" t="n"/>
       <c r="I15" s="4" t="inlineStr"/>
       <c r="J15" s="4" t="inlineStr"/>
       <c r="K15" s="4" t="inlineStr"/>
       <c r="L15" s="4" t="inlineStr"/>
-      <c r="M15" s="28" t="inlineStr">
-        <is>
-          <t>DA265 (C405)</t>
-        </is>
-      </c>
-      <c r="N15" s="28" t="n"/>
+      <c r="M15" s="25" t="inlineStr">
+        <is>
+          <t>HS261 (C403)</t>
+        </is>
+      </c>
+      <c r="N15" s="25" t="n"/>
       <c r="O15" s="4" t="inlineStr"/>
       <c r="P15" s="4" t="inlineStr"/>
       <c r="Q15" s="4" t="inlineStr"/>
@@ -10853,34 +10877,34 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Tuesday</t>
+          <t>Thursday</t>
         </is>
       </c>
       <c r="B16" s="4" t="inlineStr"/>
-      <c r="C16" s="11" t="inlineStr">
-        <is>
-          <t>Elective2</t>
-        </is>
-      </c>
-      <c r="D16" s="11" t="n"/>
+      <c r="C16" s="29" t="inlineStr">
+        <is>
+          <t>DA263 (C403)</t>
+        </is>
+      </c>
+      <c r="D16" s="29" t="n"/>
       <c r="E16" s="4" t="inlineStr"/>
       <c r="F16" s="27" t="inlineStr">
         <is>
-          <t>DA264 (C404)</t>
+          <t>DA264 (Lab-L406)</t>
         </is>
       </c>
       <c r="G16" s="27" t="n"/>
       <c r="H16" s="27" t="n"/>
-      <c r="I16" s="28" t="inlineStr">
-        <is>
-          <t>DA265T (C405)</t>
-        </is>
-      </c>
-      <c r="J16" s="28" t="n"/>
-      <c r="K16" s="28" t="n"/>
+      <c r="I16" s="27" t="n"/>
+      <c r="J16" s="27" t="n"/>
+      <c r="K16" s="4" t="inlineStr"/>
       <c r="L16" s="4" t="inlineStr"/>
-      <c r="M16" s="4" t="inlineStr"/>
-      <c r="N16" s="4" t="inlineStr"/>
+      <c r="M16" s="25" t="inlineStr">
+        <is>
+          <t>HS261 (C403)</t>
+        </is>
+      </c>
+      <c r="N16" s="25" t="n"/>
       <c r="O16" s="4" t="inlineStr"/>
       <c r="P16" s="4" t="inlineStr"/>
       <c r="Q16" s="4" t="inlineStr"/>
@@ -10891,34 +10915,30 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Wednesday</t>
+          <t>Friday</t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr"/>
-      <c r="C17" s="11" t="inlineStr">
-        <is>
-          <t>Elective2T</t>
-        </is>
-      </c>
-      <c r="D17" s="4" t="inlineStr"/>
+      <c r="C17" s="28" t="inlineStr">
+        <is>
+          <t>DA265 (C405)</t>
+        </is>
+      </c>
+      <c r="D17" s="28" t="n"/>
       <c r="E17" s="4" t="inlineStr"/>
-      <c r="F17" s="27" t="inlineStr">
-        <is>
-          <t>DA264 (C404)</t>
-        </is>
-      </c>
-      <c r="G17" s="27" t="n"/>
-      <c r="H17" s="27" t="n"/>
+      <c r="F17" s="29" t="inlineStr">
+        <is>
+          <t>DA263 (C403)</t>
+        </is>
+      </c>
+      <c r="G17" s="29" t="n"/>
+      <c r="H17" s="29" t="n"/>
       <c r="I17" s="4" t="inlineStr"/>
       <c r="J17" s="4" t="inlineStr"/>
       <c r="K17" s="4" t="inlineStr"/>
       <c r="L17" s="4" t="inlineStr"/>
-      <c r="M17" s="25" t="inlineStr">
-        <is>
-          <t>HS261 (C403)</t>
-        </is>
-      </c>
-      <c r="N17" s="25" t="n"/>
+      <c r="M17" s="4" t="inlineStr"/>
+      <c r="N17" s="4" t="inlineStr"/>
       <c r="O17" s="4" t="inlineStr"/>
       <c r="P17" s="4" t="inlineStr"/>
       <c r="Q17" s="4" t="inlineStr"/>
@@ -10927,83 +10947,51 @@
       <c r="T17" s="4" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>Thursday</t>
-        </is>
-      </c>
-      <c r="B18" s="4" t="inlineStr"/>
-      <c r="C18" s="29" t="inlineStr">
-        <is>
-          <t>DA263 (C403)</t>
-        </is>
-      </c>
-      <c r="D18" s="29" t="n"/>
-      <c r="E18" s="4" t="inlineStr"/>
-      <c r="F18" s="27" t="inlineStr">
-        <is>
-          <t>DA264 (Lab-L406)</t>
-        </is>
-      </c>
-      <c r="G18" s="27" t="n"/>
-      <c r="H18" s="27" t="n"/>
-      <c r="I18" s="27" t="n"/>
-      <c r="J18" s="27" t="n"/>
-      <c r="K18" s="4" t="inlineStr"/>
-      <c r="L18" s="4" t="inlineStr"/>
-      <c r="M18" s="25" t="inlineStr">
-        <is>
-          <t>HS261 (C403)</t>
-        </is>
-      </c>
-      <c r="N18" s="25" t="n"/>
-      <c r="O18" s="4" t="inlineStr"/>
-      <c r="P18" s="4" t="inlineStr"/>
-      <c r="Q18" s="4" t="inlineStr"/>
-      <c r="R18" s="4" t="inlineStr"/>
-      <c r="S18" s="4" t="inlineStr"/>
-      <c r="T18" s="4" t="inlineStr"/>
+      <c r="A18" t="inlineStr"/>
+      <c r="B18" s="4" t="n"/>
+      <c r="C18" s="4" t="n"/>
+      <c r="D18" s="4" t="n"/>
+      <c r="E18" s="4" t="n"/>
+      <c r="F18" s="4" t="n"/>
+      <c r="G18" s="4" t="n"/>
+      <c r="H18" s="4" t="n"/>
+      <c r="I18" s="4" t="n"/>
+      <c r="J18" s="4" t="n"/>
+      <c r="K18" s="4" t="n"/>
+      <c r="L18" s="4" t="n"/>
+      <c r="M18" s="4" t="n"/>
+      <c r="N18" s="4" t="n"/>
+      <c r="O18" s="4" t="n"/>
+      <c r="P18" s="4" t="n"/>
+      <c r="Q18" s="4" t="n"/>
+      <c r="R18" s="4" t="n"/>
+      <c r="S18" s="4" t="n"/>
+      <c r="T18" s="4" t="n"/>
     </row>
     <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>Friday</t>
-        </is>
-      </c>
-      <c r="B19" s="4" t="inlineStr"/>
-      <c r="C19" s="28" t="inlineStr">
-        <is>
-          <t>DA265 (C405)</t>
-        </is>
-      </c>
-      <c r="D19" s="28" t="n"/>
-      <c r="E19" s="4" t="inlineStr"/>
-      <c r="F19" s="29" t="inlineStr">
-        <is>
-          <t>DA263 (C403)</t>
-        </is>
-      </c>
-      <c r="G19" s="29" t="n"/>
-      <c r="H19" s="29" t="n"/>
-      <c r="I19" s="4" t="inlineStr"/>
-      <c r="J19" s="4" t="inlineStr"/>
-      <c r="K19" s="4" t="inlineStr"/>
-      <c r="L19" s="4" t="inlineStr"/>
-      <c r="M19" s="4" t="inlineStr"/>
-      <c r="N19" s="4" t="inlineStr"/>
-      <c r="O19" s="4" t="inlineStr"/>
-      <c r="P19" s="4" t="inlineStr"/>
-      <c r="Q19" s="4" t="inlineStr"/>
-      <c r="R19" s="4" t="inlineStr"/>
-      <c r="S19" s="4" t="inlineStr"/>
-      <c r="T19" s="4" t="inlineStr"/>
+      <c r="A19" t="inlineStr"/>
+      <c r="B19" s="4" t="n"/>
+      <c r="C19" s="4" t="n"/>
+      <c r="D19" s="4" t="n"/>
+      <c r="E19" s="4" t="n"/>
+      <c r="F19" s="4" t="n"/>
+      <c r="G19" s="4" t="n"/>
+      <c r="H19" s="4" t="n"/>
+      <c r="I19" s="4" t="n"/>
+      <c r="J19" s="4" t="n"/>
+      <c r="K19" s="4" t="n"/>
+      <c r="L19" s="4" t="n"/>
+      <c r="M19" s="4" t="n"/>
+      <c r="N19" s="4" t="n"/>
+      <c r="O19" s="4" t="n"/>
+      <c r="P19" s="4" t="n"/>
+      <c r="Q19" s="4" t="n"/>
+      <c r="R19" s="4" t="n"/>
+      <c r="S19" s="4" t="n"/>
+      <c r="T19" s="4" t="n"/>
     </row>
     <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>WARNING: Courses missing from generated timetable output</t>
-        </is>
-      </c>
+      <c r="A20" t="inlineStr"/>
       <c r="B20" s="4" t="n"/>
       <c r="C20" s="4" t="n"/>
       <c r="D20" s="4" t="n"/>
@@ -11025,9 +11013,9 @@
       <c r="T20" s="4" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>DS308: combined-course constraints prevented placement</t>
+      <c r="A21" s="13" t="inlineStr">
+        <is>
+          <t>Legend - DSAI IV</t>
         </is>
       </c>
       <c r="B21" s="4" t="n"/>
@@ -11051,14 +11039,46 @@
       <c r="T21" s="4" t="n"/>
     </row>
     <row r="22">
-      <c r="A22" t="inlineStr"/>
-      <c r="B22" s="4" t="n"/>
-      <c r="C22" s="4" t="n"/>
-      <c r="D22" s="4" t="n"/>
-      <c r="E22" s="4" t="n"/>
-      <c r="F22" s="4" t="n"/>
-      <c r="G22" s="4" t="n"/>
-      <c r="H22" s="4" t="n"/>
+      <c r="A22" s="14" t="inlineStr">
+        <is>
+          <t>Course Code</t>
+        </is>
+      </c>
+      <c r="B22" s="15" t="inlineStr">
+        <is>
+          <t>Course Title</t>
+        </is>
+      </c>
+      <c r="C22" s="15" t="inlineStr">
+        <is>
+          <t>L-T-P-S-C</t>
+        </is>
+      </c>
+      <c r="D22" s="15" t="inlineStr">
+        <is>
+          <t>Faculty</t>
+        </is>
+      </c>
+      <c r="E22" s="15" t="inlineStr">
+        <is>
+          <t>Semester Half</t>
+        </is>
+      </c>
+      <c r="F22" s="16" t="inlineStr">
+        <is>
+          <t>Elective</t>
+        </is>
+      </c>
+      <c r="G22" s="16" t="inlineStr">
+        <is>
+          <t>Elective Basket</t>
+        </is>
+      </c>
+      <c r="H22" s="16" t="inlineStr">
+        <is>
+          <t>Elective Room</t>
+        </is>
+      </c>
       <c r="I22" s="4" t="n"/>
       <c r="J22" s="4" t="n"/>
       <c r="K22" s="4" t="n"/>
@@ -11073,14 +11093,42 @@
       <c r="T22" s="4" t="n"/>
     </row>
     <row r="23">
-      <c r="A23" t="inlineStr"/>
-      <c r="B23" s="4" t="n"/>
-      <c r="C23" s="4" t="n"/>
-      <c r="D23" s="4" t="n"/>
-      <c r="E23" s="4" t="n"/>
-      <c r="F23" s="4" t="n"/>
-      <c r="G23" s="4" t="n"/>
-      <c r="H23" s="4" t="n"/>
+      <c r="A23" s="17" t="inlineStr">
+        <is>
+          <t>DA263</t>
+        </is>
+      </c>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>Big Data Analytics</t>
+        </is>
+      </c>
+      <c r="C23" s="3" t="inlineStr">
+        <is>
+          <t>3-1-0-0-4</t>
+        </is>
+      </c>
+      <c r="D23" s="3" t="inlineStr">
+        <is>
+          <t>Dr. Animesh Chaturvedi</t>
+        </is>
+      </c>
+      <c r="E23" s="3" t="inlineStr">
+        <is>
+          <t>Full Sem</t>
+        </is>
+      </c>
+      <c r="F23" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G23" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H23" s="4" t="inlineStr"/>
       <c r="I23" s="4" t="n"/>
       <c r="J23" s="4" t="n"/>
       <c r="K23" s="4" t="n"/>
@@ -11095,14 +11143,42 @@
       <c r="T23" s="4" t="n"/>
     </row>
     <row r="24">
-      <c r="A24" t="inlineStr"/>
-      <c r="B24" s="4" t="n"/>
-      <c r="C24" s="4" t="n"/>
-      <c r="D24" s="4" t="n"/>
-      <c r="E24" s="4" t="n"/>
-      <c r="F24" s="4" t="n"/>
-      <c r="G24" s="4" t="n"/>
-      <c r="H24" s="4" t="n"/>
+      <c r="A24" s="17" t="inlineStr">
+        <is>
+          <t>DA264</t>
+        </is>
+      </c>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>Database Management and Warehousing</t>
+        </is>
+      </c>
+      <c r="C24" s="3" t="inlineStr">
+        <is>
+          <t>3-0-2-0-4</t>
+        </is>
+      </c>
+      <c r="D24" s="3" t="inlineStr">
+        <is>
+          <t>Dr. Utkarsh Mahadeo Khaire</t>
+        </is>
+      </c>
+      <c r="E24" s="3" t="inlineStr">
+        <is>
+          <t>Full Sem</t>
+        </is>
+      </c>
+      <c r="F24" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G24" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H24" s="4" t="inlineStr"/>
       <c r="I24" s="4" t="n"/>
       <c r="J24" s="4" t="n"/>
       <c r="K24" s="4" t="n"/>
@@ -11117,18 +11193,42 @@
       <c r="T24" s="4" t="n"/>
     </row>
     <row r="25">
-      <c r="A25" s="13" t="inlineStr">
-        <is>
-          <t>Legend - DSAI IV</t>
-        </is>
-      </c>
-      <c r="B25" s="4" t="n"/>
-      <c r="C25" s="4" t="n"/>
-      <c r="D25" s="4" t="n"/>
-      <c r="E25" s="4" t="n"/>
-      <c r="F25" s="4" t="n"/>
-      <c r="G25" s="4" t="n"/>
-      <c r="H25" s="4" t="n"/>
+      <c r="A25" s="17" t="inlineStr">
+        <is>
+          <t>DA265</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>Deep Learning</t>
+        </is>
+      </c>
+      <c r="C25" s="3" t="inlineStr">
+        <is>
+          <t>3-1-0-0-4</t>
+        </is>
+      </c>
+      <c r="D25" s="3" t="inlineStr">
+        <is>
+          <t>Dr. Shirshendu Layek</t>
+        </is>
+      </c>
+      <c r="E25" s="3" t="inlineStr">
+        <is>
+          <t>Full Sem</t>
+        </is>
+      </c>
+      <c r="F25" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G25" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H25" s="4" t="inlineStr"/>
       <c r="I25" s="4" t="n"/>
       <c r="J25" s="4" t="n"/>
       <c r="K25" s="4" t="n"/>
@@ -11143,46 +11243,42 @@
       <c r="T25" s="4" t="n"/>
     </row>
     <row r="26">
-      <c r="A26" s="14" t="inlineStr">
-        <is>
-          <t>Course Code</t>
-        </is>
-      </c>
-      <c r="B26" s="15" t="inlineStr">
-        <is>
-          <t>Course Title</t>
-        </is>
-      </c>
-      <c r="C26" s="15" t="inlineStr">
-        <is>
-          <t>L-T-P-S-C</t>
-        </is>
-      </c>
-      <c r="D26" s="15" t="inlineStr">
-        <is>
-          <t>Faculty</t>
-        </is>
-      </c>
-      <c r="E26" s="15" t="inlineStr">
-        <is>
-          <t>Semester Half</t>
-        </is>
-      </c>
-      <c r="F26" s="16" t="inlineStr">
-        <is>
-          <t>Elective</t>
-        </is>
-      </c>
-      <c r="G26" s="16" t="inlineStr">
-        <is>
-          <t>Elective Basket</t>
-        </is>
-      </c>
-      <c r="H26" s="16" t="inlineStr">
-        <is>
-          <t>Elective Room</t>
-        </is>
-      </c>
+      <c r="A26" s="17" t="inlineStr">
+        <is>
+          <t>DS308</t>
+        </is>
+      </c>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>Data Security and Privacy</t>
+        </is>
+      </c>
+      <c r="C26" s="3" t="inlineStr">
+        <is>
+          <t>3-1-0-4-4</t>
+        </is>
+      </c>
+      <c r="D26" s="3" t="inlineStr">
+        <is>
+          <t>Dr. Girish Revadigar</t>
+        </is>
+      </c>
+      <c r="E26" s="3" t="inlineStr">
+        <is>
+          <t>Full Sem</t>
+        </is>
+      </c>
+      <c r="F26" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G26" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H26" s="4" t="inlineStr"/>
       <c r="I26" s="4" t="n"/>
       <c r="J26" s="4" t="n"/>
       <c r="K26" s="4" t="n"/>
@@ -11199,22 +11295,22 @@
     <row r="27">
       <c r="A27" s="17" t="inlineStr">
         <is>
-          <t>DA263</t>
+          <t>HS261</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>Big Data Analytics</t>
+          <t>Ethics and Values / Environmental Studies</t>
         </is>
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t>3-1-0-0-4</t>
+          <t>3-0-0-0-3</t>
         </is>
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t>Dr. Animesh Chaturvedi</t>
+          <t>Dr. Aswath Babu H</t>
         </is>
       </c>
       <c r="E27" s="3" t="inlineStr">
@@ -11249,40 +11345,44 @@
     <row r="28">
       <c r="A28" s="17" t="inlineStr">
         <is>
-          <t>DA264</t>
+          <t>EC255</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>Database Management and Warehousing</t>
+          <t>Embedded Intelligent Sensing Systems</t>
         </is>
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t>3-0-2-0-4</t>
+          <t>2-0-2-4-2</t>
         </is>
       </c>
       <c r="D28" s="3" t="inlineStr">
         <is>
-          <t>Dr. Utkarsh Mahadeo Khaire</t>
+          <t>Dr. Sibasankar Padhy</t>
         </is>
       </c>
       <c r="E28" s="3" t="inlineStr">
         <is>
-          <t>Full Sem</t>
+          <t>First Half</t>
         </is>
       </c>
       <c r="F28" s="3" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G28" s="3" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H28" s="4" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H28" s="3" t="inlineStr">
+        <is>
+          <t>C301</t>
+        </is>
+      </c>
       <c r="I28" s="4" t="n"/>
       <c r="J28" s="4" t="n"/>
       <c r="K28" s="4" t="n"/>
@@ -11299,40 +11399,44 @@
     <row r="29">
       <c r="A29" s="17" t="inlineStr">
         <is>
-          <t>DA265</t>
+          <t>NEW</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>Deep Learning</t>
+          <t>Edge AI Systems Design</t>
         </is>
       </c>
       <c r="C29" s="3" t="inlineStr">
         <is>
-          <t>3-1-0-0-4</t>
+          <t>3-1-0-0-2</t>
         </is>
       </c>
       <c r="D29" s="3" t="inlineStr">
         <is>
-          <t>Dr. Shirshendu Layek</t>
+          <t>Dr. Deepak K T</t>
         </is>
       </c>
       <c r="E29" s="3" t="inlineStr">
         <is>
-          <t>Full Sem</t>
+          <t>First Half</t>
         </is>
       </c>
       <c r="F29" s="3" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G29" s="3" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H29" s="4" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H29" s="3" t="inlineStr">
+        <is>
+          <t>C102</t>
+        </is>
+      </c>
       <c r="I29" s="4" t="n"/>
       <c r="J29" s="4" t="n"/>
       <c r="K29" s="4" t="n"/>
@@ -11349,40 +11453,44 @@
     <row r="30">
       <c r="A30" s="17" t="inlineStr">
         <is>
-          <t>DS308</t>
+          <t>CS252</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>Data Security and Privacy</t>
+          <t>Digital Forensic</t>
         </is>
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
-          <t>3-1-0-4-4</t>
+          <t>3-1-0-0-2</t>
         </is>
       </c>
       <c r="D30" s="3" t="inlineStr">
         <is>
-          <t>Dr. Girish Revadigar</t>
+          <t>Dr. Abdul Wahid</t>
         </is>
       </c>
       <c r="E30" s="3" t="inlineStr">
         <is>
-          <t>Full Sem</t>
+          <t>Second Half</t>
         </is>
       </c>
       <c r="F30" s="3" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G30" s="3" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H30" s="4" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H30" s="3" t="inlineStr">
+        <is>
+          <t>C401</t>
+        </is>
+      </c>
       <c r="I30" s="4" t="n"/>
       <c r="J30" s="4" t="n"/>
       <c r="K30" s="4" t="n"/>
@@ -11399,40 +11507,44 @@
     <row r="31">
       <c r="A31" s="17" t="inlineStr">
         <is>
-          <t>HS261</t>
+          <t>CS261</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>Ethics and Values / Environmental Studies</t>
+          <t>Operating System</t>
         </is>
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t>3-0-0-0-3</t>
+          <t>3-1-0-0-2</t>
         </is>
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t>Dr. Aswath Babu H</t>
+          <t>Dr. Siddharth R</t>
         </is>
       </c>
       <c r="E31" s="3" t="inlineStr">
         <is>
-          <t>Full Sem</t>
+          <t>Second Half</t>
         </is>
       </c>
       <c r="F31" s="3" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G31" s="3" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H31" s="4" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H31" s="3" t="inlineStr">
+        <is>
+          <t>C003</t>
+        </is>
+      </c>
       <c r="I31" s="4" t="n"/>
       <c r="J31" s="4" t="n"/>
       <c r="K31" s="4" t="n"/>
@@ -11449,27 +11561,27 @@
     <row r="32">
       <c r="A32" s="17" t="inlineStr">
         <is>
-          <t>EC255</t>
+          <t>EC257</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>Embedded Intelligent Sensing Systems</t>
+          <t>Causal Inference</t>
         </is>
       </c>
       <c r="C32" s="3" t="inlineStr">
         <is>
-          <t>2-0-2-4-2</t>
+          <t>3-1-0-0-2</t>
         </is>
       </c>
       <c r="D32" s="3" t="inlineStr">
         <is>
-          <t>Dr. Sibasankar Padhy</t>
+          <t>Dr. Chinmayananda A</t>
         </is>
       </c>
       <c r="E32" s="3" t="inlineStr">
         <is>
-          <t>First Half</t>
+          <t>Second Half</t>
         </is>
       </c>
       <c r="F32" s="3" t="inlineStr">
@@ -11479,12 +11591,12 @@
       </c>
       <c r="G32" s="3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="H32" s="3" t="inlineStr">
         <is>
-          <t>C301</t>
+          <t>C302</t>
         </is>
       </c>
       <c r="I32" s="4" t="n"/>
@@ -11503,12 +11615,12 @@
     <row r="33">
       <c r="A33" s="17" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>CS253</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>Edge AI Systems Design</t>
+          <t>Time Series Forecasting and Applications</t>
         </is>
       </c>
       <c r="C33" s="3" t="inlineStr">
@@ -11518,12 +11630,12 @@
       </c>
       <c r="D33" s="3" t="inlineStr">
         <is>
-          <t>Dr. Deepak K T</t>
+          <t>Dr. Nataraj</t>
         </is>
       </c>
       <c r="E33" s="3" t="inlineStr">
         <is>
-          <t>First Half</t>
+          <t>Second Half</t>
         </is>
       </c>
       <c r="F33" s="3" t="inlineStr">
@@ -11533,12 +11645,12 @@
       </c>
       <c r="G33" s="3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="H33" s="3" t="inlineStr">
         <is>
-          <t>C102</t>
+          <t>C303</t>
         </is>
       </c>
       <c r="I33" s="4" t="n"/>
@@ -11555,46 +11667,14 @@
       <c r="T33" s="4" t="n"/>
     </row>
     <row r="34">
-      <c r="A34" s="17" t="inlineStr">
-        <is>
-          <t>CS252</t>
-        </is>
-      </c>
-      <c r="B34" s="3" t="inlineStr">
-        <is>
-          <t>Digital Forensic</t>
-        </is>
-      </c>
-      <c r="C34" s="3" t="inlineStr">
-        <is>
-          <t>3-1-0-0-2</t>
-        </is>
-      </c>
-      <c r="D34" s="3" t="inlineStr">
-        <is>
-          <t>Dr. Abdul Wahid</t>
-        </is>
-      </c>
-      <c r="E34" s="3" t="inlineStr">
-        <is>
-          <t>Second Half</t>
-        </is>
-      </c>
-      <c r="F34" s="3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G34" s="3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="H34" s="3" t="inlineStr">
-        <is>
-          <t>C401</t>
-        </is>
-      </c>
+      <c r="A34" t="inlineStr"/>
+      <c r="B34" s="4" t="n"/>
+      <c r="C34" s="4" t="n"/>
+      <c r="D34" s="4" t="n"/>
+      <c r="E34" s="4" t="n"/>
+      <c r="F34" s="4" t="n"/>
+      <c r="G34" s="4" t="n"/>
+      <c r="H34" s="4" t="n"/>
       <c r="I34" s="4" t="n"/>
       <c r="J34" s="4" t="n"/>
       <c r="K34" s="4" t="n"/>
@@ -11608,216 +11688,32 @@
       <c r="S34" s="4" t="n"/>
       <c r="T34" s="4" t="n"/>
     </row>
-    <row r="35">
-      <c r="A35" s="17" t="inlineStr">
-        <is>
-          <t>CS261</t>
-        </is>
-      </c>
-      <c r="B35" s="3" t="inlineStr">
-        <is>
-          <t>Operating System</t>
-        </is>
-      </c>
-      <c r="C35" s="3" t="inlineStr">
-        <is>
-          <t>3-1-0-0-2</t>
-        </is>
-      </c>
-      <c r="D35" s="3" t="inlineStr">
-        <is>
-          <t>Dr. Siddharth R</t>
-        </is>
-      </c>
-      <c r="E35" s="3" t="inlineStr">
-        <is>
-          <t>Second Half</t>
-        </is>
-      </c>
-      <c r="F35" s="3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G35" s="3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="H35" s="3" t="inlineStr">
-        <is>
-          <t>C003</t>
-        </is>
-      </c>
-      <c r="I35" s="4" t="n"/>
-      <c r="J35" s="4" t="n"/>
-      <c r="K35" s="4" t="n"/>
-      <c r="L35" s="4" t="n"/>
-      <c r="M35" s="4" t="n"/>
-      <c r="N35" s="4" t="n"/>
-      <c r="O35" s="4" t="n"/>
-      <c r="P35" s="4" t="n"/>
-      <c r="Q35" s="4" t="n"/>
-      <c r="R35" s="4" t="n"/>
-      <c r="S35" s="4" t="n"/>
-      <c r="T35" s="4" t="n"/>
-    </row>
-    <row r="36">
-      <c r="A36" s="17" t="inlineStr">
-        <is>
-          <t>EC257</t>
-        </is>
-      </c>
-      <c r="B36" s="3" t="inlineStr">
-        <is>
-          <t>Causal Inference</t>
-        </is>
-      </c>
-      <c r="C36" s="3" t="inlineStr">
-        <is>
-          <t>3-1-0-0-2</t>
-        </is>
-      </c>
-      <c r="D36" s="3" t="inlineStr">
-        <is>
-          <t>Dr. Chinmayananda A</t>
-        </is>
-      </c>
-      <c r="E36" s="3" t="inlineStr">
-        <is>
-          <t>Second Half</t>
-        </is>
-      </c>
-      <c r="F36" s="3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G36" s="3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="H36" s="3" t="inlineStr">
-        <is>
-          <t>C302</t>
-        </is>
-      </c>
-      <c r="I36" s="4" t="n"/>
-      <c r="J36" s="4" t="n"/>
-      <c r="K36" s="4" t="n"/>
-      <c r="L36" s="4" t="n"/>
-      <c r="M36" s="4" t="n"/>
-      <c r="N36" s="4" t="n"/>
-      <c r="O36" s="4" t="n"/>
-      <c r="P36" s="4" t="n"/>
-      <c r="Q36" s="4" t="n"/>
-      <c r="R36" s="4" t="n"/>
-      <c r="S36" s="4" t="n"/>
-      <c r="T36" s="4" t="n"/>
-    </row>
-    <row r="37">
-      <c r="A37" s="17" t="inlineStr">
-        <is>
-          <t>CS253</t>
-        </is>
-      </c>
-      <c r="B37" s="3" t="inlineStr">
-        <is>
-          <t>Time Series Forecasting and Applications</t>
-        </is>
-      </c>
-      <c r="C37" s="3" t="inlineStr">
-        <is>
-          <t>3-1-0-0-2</t>
-        </is>
-      </c>
-      <c r="D37" s="3" t="inlineStr">
-        <is>
-          <t>Dr. Nataraj</t>
-        </is>
-      </c>
-      <c r="E37" s="3" t="inlineStr">
-        <is>
-          <t>Second Half</t>
-        </is>
-      </c>
-      <c r="F37" s="3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G37" s="3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="H37" s="3" t="inlineStr">
-        <is>
-          <t>C303</t>
-        </is>
-      </c>
-      <c r="I37" s="4" t="n"/>
-      <c r="J37" s="4" t="n"/>
-      <c r="K37" s="4" t="n"/>
-      <c r="L37" s="4" t="n"/>
-      <c r="M37" s="4" t="n"/>
-      <c r="N37" s="4" t="n"/>
-      <c r="O37" s="4" t="n"/>
-      <c r="P37" s="4" t="n"/>
-      <c r="Q37" s="4" t="n"/>
-      <c r="R37" s="4" t="n"/>
-      <c r="S37" s="4" t="n"/>
-      <c r="T37" s="4" t="n"/>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr"/>
-      <c r="B38" s="4" t="n"/>
-      <c r="C38" s="4" t="n"/>
-      <c r="D38" s="4" t="n"/>
-      <c r="E38" s="4" t="n"/>
-      <c r="F38" s="4" t="n"/>
-      <c r="G38" s="4" t="n"/>
-      <c r="H38" s="4" t="n"/>
-      <c r="I38" s="4" t="n"/>
-      <c r="J38" s="4" t="n"/>
-      <c r="K38" s="4" t="n"/>
-      <c r="L38" s="4" t="n"/>
-      <c r="M38" s="4" t="n"/>
-      <c r="N38" s="4" t="n"/>
-      <c r="O38" s="4" t="n"/>
-      <c r="P38" s="4" t="n"/>
-      <c r="Q38" s="4" t="n"/>
-      <c r="R38" s="4" t="n"/>
-      <c r="S38" s="4" t="n"/>
-      <c r="T38" s="4" t="n"/>
-    </row>
   </sheetData>
   <mergeCells count="26">
-    <mergeCell ref="I16:K16"/>
     <mergeCell ref="C6:D6"/>
     <mergeCell ref="F5:H5"/>
-    <mergeCell ref="C15:D15"/>
     <mergeCell ref="O4:Q4"/>
+    <mergeCell ref="F16:J16"/>
     <mergeCell ref="C5:D5"/>
     <mergeCell ref="F8:H8"/>
+    <mergeCell ref="C14:D14"/>
     <mergeCell ref="M5:N5"/>
     <mergeCell ref="F17:H17"/>
     <mergeCell ref="F6:J6"/>
-    <mergeCell ref="C18:D18"/>
     <mergeCell ref="C4:D4"/>
     <mergeCell ref="C16:D16"/>
-    <mergeCell ref="F15:G15"/>
-    <mergeCell ref="F18:J18"/>
+    <mergeCell ref="I14:K14"/>
+    <mergeCell ref="M13:N13"/>
+    <mergeCell ref="M16:N16"/>
     <mergeCell ref="M15:N15"/>
+    <mergeCell ref="F14:H14"/>
     <mergeCell ref="M6:N6"/>
-    <mergeCell ref="M18:N18"/>
-    <mergeCell ref="M17:N17"/>
-    <mergeCell ref="F16:H16"/>
+    <mergeCell ref="F13:G13"/>
+    <mergeCell ref="C17:D17"/>
     <mergeCell ref="C7:D7"/>
-    <mergeCell ref="F19:H19"/>
-    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="C13:D13"/>
     <mergeCell ref="F7:H7"/>
+    <mergeCell ref="F15:H15"/>
     <mergeCell ref="M4:N4"/>
     <mergeCell ref="F4:J4"/>
   </mergeCells>
